--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-08.xlsx
@@ -1063,7 +1063,7 @@
     <t>Atletico Grau</t>
   </si>
   <si>
-    <t>2026-08-06 01:35:02</t>
+    <t>2026-08-06 03:47:07</t>
   </si>
 </sst>
 </file>
@@ -1657,226 +1657,226 @@
         <v>248</v>
       </c>
       <c r="F2">
-        <v>1.37</v>
+        <v>2.62</v>
       </c>
       <c r="G2">
-        <v>600</v>
+        <v>3.05</v>
       </c>
       <c r="H2">
-        <v>1.37</v>
+        <v>2.68</v>
       </c>
       <c r="I2">
-        <v>870</v>
+        <v>3.05</v>
       </c>
       <c r="J2">
-        <v>1.51</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M2">
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>1.05</v>
+        <v>3.35</v>
       </c>
       <c r="O2">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>1.81</v>
       </c>
       <c r="Q2">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="T2">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="CB2" t="s">
         <v>349</v>
@@ -1899,166 +1899,166 @@
         <v>249</v>
       </c>
       <c r="F3">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G3">
         <v>1.35</v>
       </c>
       <c r="H3">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
-        <v>870</v>
+        <v>12.5</v>
       </c>
       <c r="J3">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="K3">
-        <v>950</v>
+        <v>6.8</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="O3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P3">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Q3">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2141,22 +2141,22 @@
         <v>250</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>1.59</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J4">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -2383,46 +2383,46 @@
         <v>251</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="G5">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I5">
-        <v>870</v>
+        <v>5.3</v>
       </c>
       <c r="J5">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P5">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q5">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -2431,130 +2431,130 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
@@ -2563,37 +2563,37 @@
         <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS5">
         <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU5">
         <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY5">
         <v>1.01</v>
@@ -2625,22 +2625,22 @@
         <v>252</v>
       </c>
       <c r="F6">
-        <v>1.71</v>
+        <v>4.4</v>
       </c>
       <c r="G6">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>1.26</v>
+        <v>2.02</v>
       </c>
       <c r="I6">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K6">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2867,22 +2867,22 @@
         <v>253</v>
       </c>
       <c r="F7">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="G7">
-        <v>3.3</v>
+        <v>2.72</v>
       </c>
       <c r="H7">
-        <v>1.36</v>
+        <v>3.1</v>
       </c>
       <c r="I7">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="J7">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="K7">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2897,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q7">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -3109,40 +3109,40 @@
         <v>254</v>
       </c>
       <c r="F8">
+        <v>2.1</v>
+      </c>
+      <c r="G8">
+        <v>2.28</v>
+      </c>
+      <c r="H8">
+        <v>3.4</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>3.5</v>
+      </c>
+      <c r="K8">
+        <v>3.85</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
         <v>1.92</v>
       </c>
-      <c r="G8">
-        <v>2.62</v>
-      </c>
-      <c r="H8">
-        <v>1.33</v>
-      </c>
-      <c r="I8">
-        <v>4.8</v>
-      </c>
-      <c r="J8">
-        <v>2.72</v>
-      </c>
-      <c r="K8">
-        <v>950</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>1.25</v>
-      </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -3351,22 +3351,22 @@
         <v>255</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="G9">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="I9">
-        <v>50</v>
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="K9">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3381,10 +3381,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3593,22 +3593,22 @@
         <v>256</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>1.87</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="I10">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="J10">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="K10">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3623,10 +3623,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3835,22 +3835,22 @@
         <v>257</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H11">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3865,10 +3865,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -4077,22 +4077,22 @@
         <v>258</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="K12">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -4107,10 +4107,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -4319,22 +4319,22 @@
         <v>259</v>
       </c>
       <c r="F13">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H13">
-        <v>1.04</v>
+        <v>2.84</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4349,10 +4349,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="Q13">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4564,16 +4564,16 @@
         <v>1.04</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="H14">
         <v>1.04</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="J14">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -4585,16 +4585,16 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P14">
         <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R14">
         <v>1.25</v>
@@ -4609,10 +4609,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4806,16 +4806,16 @@
         <v>1.04</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="H15">
         <v>1.04</v>
       </c>
       <c r="I15">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="J15">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K15">
         <v>950</v>
@@ -4827,22 +4827,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O15">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
         <v>1.25</v>
       </c>
       <c r="Q15">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="R15">
         <v>1.25</v>
       </c>
       <c r="S15">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4851,10 +4851,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -5045,19 +5045,19 @@
         <v>262</v>
       </c>
       <c r="F16">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="G16">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="H16">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="I16">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
         <v>4.5</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q16">
-        <v>1.32</v>
+        <v>1.68</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -5087,10 +5087,10 @@
         <v>0</v>
       </c>
       <c r="T16">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -5099,112 +5099,112 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH16">
         <v>0</v>
@@ -5287,19 +5287,19 @@
         <v>263</v>
       </c>
       <c r="F17">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>2.42</v>
       </c>
       <c r="H17">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="I17">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J17">
-        <v>2.08</v>
+        <v>3.8</v>
       </c>
       <c r="K17">
         <v>3.9</v>
@@ -5317,7 +5317,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q17">
         <v>1.6</v>
@@ -5329,10 +5329,10 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -5341,112 +5341,112 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA17">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB17">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE17">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI17">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO17">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS17">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH17">
         <v>0</v>
@@ -5529,19 +5529,19 @@
         <v>264</v>
       </c>
       <c r="F18">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="G18">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="H18">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="I18">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J18">
-        <v>1.53</v>
+        <v>3.8</v>
       </c>
       <c r="K18">
         <v>4.2</v>
@@ -5559,10 +5559,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5571,10 +5571,10 @@
         <v>0</v>
       </c>
       <c r="T18">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="V18">
         <v>0</v>
@@ -5583,112 +5583,112 @@
         <v>0</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH18">
         <v>0</v>
@@ -5771,22 +5771,22 @@
         <v>265</v>
       </c>
       <c r="F19">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="H19">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="I19">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="J19">
-        <v>1.23</v>
+        <v>4.4</v>
       </c>
       <c r="K19">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>2.7</v>
       </c>
       <c r="Q19">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>1.66</v>
       </c>
       <c r="G20">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="H20">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="I20">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J20">
         <v>4.1</v>
@@ -6043,10 +6043,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q20">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6055,10 +6055,10 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -6067,112 +6067,112 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH20">
         <v>0</v>
@@ -6497,22 +6497,22 @@
         <v>268</v>
       </c>
       <c r="F22">
-        <v>1.04</v>
+        <v>1.7</v>
       </c>
       <c r="G22">
-        <v>1000</v>
+        <v>1.84</v>
       </c>
       <c r="H22">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I22">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J22">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="K22">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6527,10 +6527,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>2.76</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6739,22 +6739,22 @@
         <v>269</v>
       </c>
       <c r="F23">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G23">
         <v>1.7</v>
       </c>
       <c r="H23">
-        <v>2.42</v>
+        <v>4.9</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J23">
-        <v>2.48</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6769,10 +6769,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6781,10 +6781,10 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="V23">
         <v>0</v>
@@ -6793,112 +6793,112 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH23">
         <v>0</v>
@@ -6981,19 +6981,19 @@
         <v>270</v>
       </c>
       <c r="F24">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G24">
         <v>3.65</v>
       </c>
       <c r="H24">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I24">
-        <v>110</v>
+        <v>2.16</v>
       </c>
       <c r="J24">
-        <v>1.39</v>
+        <v>4.1</v>
       </c>
       <c r="K24">
         <v>4.6</v>
@@ -7011,10 +7011,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q24">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -7023,10 +7023,10 @@
         <v>0</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="V24">
         <v>0</v>
@@ -7035,112 +7035,112 @@
         <v>0</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BH24">
         <v>0</v>
@@ -7223,16 +7223,16 @@
         <v>271</v>
       </c>
       <c r="F25">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G25">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H25">
         <v>1.55</v>
       </c>
       <c r="I25">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J25">
         <v>5.1</v>
@@ -7253,10 +7253,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q25">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7465,22 +7465,22 @@
         <v>272</v>
       </c>
       <c r="F26">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>1.32</v>
+        <v>2.52</v>
       </c>
       <c r="I26">
-        <v>100</v>
+        <v>2.8</v>
       </c>
       <c r="J26">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K26">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q26">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7507,10 +7507,10 @@
         <v>0</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V26">
         <v>0</v>
@@ -7519,112 +7519,112 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH26">
         <v>0</v>
@@ -7707,19 +7707,19 @@
         <v>273</v>
       </c>
       <c r="F27">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="G27">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H27">
-        <v>1.33</v>
+        <v>2.66</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="J27">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K27">
         <v>4</v>
@@ -7737,10 +7737,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q27">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7949,19 +7949,19 @@
         <v>274</v>
       </c>
       <c r="F28">
-        <v>1.27</v>
+        <v>1.69</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>1.81</v>
       </c>
       <c r="H28">
-        <v>1.27</v>
+        <v>4.6</v>
       </c>
       <c r="I28">
-        <v>100</v>
+        <v>5.3</v>
       </c>
       <c r="J28">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="K28">
         <v>4.8</v>
@@ -7979,10 +7979,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q28">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -7991,10 +7991,10 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -8003,112 +8003,112 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH28">
         <v>0</v>
@@ -8191,19 +8191,19 @@
         <v>275</v>
       </c>
       <c r="F29">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G29">
         <v>1.62</v>
       </c>
       <c r="H29">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I29">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="J29">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K29">
         <v>4.8</v>
@@ -8221,10 +8221,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="Q29">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8233,10 +8233,10 @@
         <v>0</v>
       </c>
       <c r="T29">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="U29">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="V29">
         <v>0</v>
@@ -8245,112 +8245,112 @@
         <v>0</v>
       </c>
       <c r="X29">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y29">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z29">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA29">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB29">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC29">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD29">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE29">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF29">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG29">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH29">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI29">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ29">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK29">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL29">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM29">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN29">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AO29">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP29">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ29">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT29">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU29">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV29">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX29">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY29">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ29">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA29">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB29">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC29">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF29">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH29">
         <v>0</v>
@@ -8433,19 +8433,19 @@
         <v>276</v>
       </c>
       <c r="F30">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I30">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="J30">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="K30">
         <v>4.4</v>
@@ -8463,10 +8463,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="Q30">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8675,22 +8675,22 @@
         <v>277</v>
       </c>
       <c r="F31">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="G31">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H31">
-        <v>1.35</v>
+        <v>2.38</v>
       </c>
       <c r="I31">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J31">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="K31">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q31">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8917,19 +8917,19 @@
         <v>278</v>
       </c>
       <c r="F32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G32">
         <v>1000</v>
       </c>
       <c r="H32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I32">
         <v>1000</v>
       </c>
       <c r="J32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K32">
         <v>950</v>
@@ -8941,7 +8941,7 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O32">
         <v>1.01</v>
@@ -8950,13 +8950,13 @@
         <v>1.25</v>
       </c>
       <c r="Q32">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="R32">
         <v>1.25</v>
       </c>
       <c r="S32">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -9401,22 +9401,22 @@
         <v>280</v>
       </c>
       <c r="F34">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G34">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H34">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="I34">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J34">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K34">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9431,10 +9431,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q34">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9643,22 +9643,22 @@
         <v>281</v>
       </c>
       <c r="F35">
-        <v>1.04</v>
+        <v>1.61</v>
       </c>
       <c r="G35">
-        <v>1000</v>
+        <v>1.76</v>
       </c>
       <c r="H35">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I35">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J35">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K35">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9673,10 +9673,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="Q35">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9885,22 +9885,22 @@
         <v>282</v>
       </c>
       <c r="F36">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G36">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H36">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I36">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J36">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="K36">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9915,10 +9915,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q36">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -10127,22 +10127,22 @@
         <v>283</v>
       </c>
       <c r="F37">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G37">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H37">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I37">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="J37">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K37">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -10157,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q37">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -10369,22 +10369,22 @@
         <v>284</v>
       </c>
       <c r="F38">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G38">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="H38">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="I38">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J38">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="K38">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10399,10 +10399,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q38">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10611,22 +10611,22 @@
         <v>285</v>
       </c>
       <c r="F39">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="G39">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H39">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I39">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="J39">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="K39">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="Q39">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10853,22 +10853,22 @@
         <v>286</v>
       </c>
       <c r="F40">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="G40">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="H40">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="I40">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J40">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K40">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10883,10 +10883,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q40">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -11340,16 +11340,16 @@
         <v>1.04</v>
       </c>
       <c r="G42">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="H42">
         <v>1.04</v>
       </c>
       <c r="I42">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="J42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K42">
         <v>950</v>
@@ -11361,22 +11361,22 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O42">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="P42">
         <v>1.25</v>
       </c>
       <c r="Q42">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="R42">
         <v>1.25</v>
       </c>
       <c r="S42">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="T42">
         <v>1.01</v>
@@ -11385,7 +11385,7 @@
         <v>1.01</v>
       </c>
       <c r="V42">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W42">
         <v>1.01</v>
@@ -11824,16 +11824,16 @@
         <v>1.04</v>
       </c>
       <c r="G44">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="H44">
         <v>1.04</v>
       </c>
       <c r="I44">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="J44">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K44">
         <v>950</v>
@@ -11845,22 +11845,22 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O44">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P44">
         <v>1.25</v>
       </c>
       <c r="Q44">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R44">
         <v>1.25</v>
       </c>
       <c r="S44">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="T44">
         <v>1.01</v>
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="V44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -12063,22 +12063,22 @@
         <v>291</v>
       </c>
       <c r="F45">
-        <v>1.33</v>
+        <v>3.15</v>
       </c>
       <c r="G45">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H45">
-        <v>1.33</v>
+        <v>2.24</v>
       </c>
       <c r="I45">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="J45">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K45">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -12093,10 +12093,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q45">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -12308,19 +12308,19 @@
         <v>2</v>
       </c>
       <c r="G46">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H46">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I46">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J46">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="K46">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -12335,10 +12335,10 @@
         <v>0</v>
       </c>
       <c r="P46">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q46">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R46">
         <v>0</v>
@@ -12547,7 +12547,7 @@
         <v>293</v>
       </c>
       <c r="F47">
-        <v>1.36</v>
+        <v>4.1</v>
       </c>
       <c r="G47">
         <v>4.4</v>
@@ -12559,10 +12559,10 @@
         <v>2.08</v>
       </c>
       <c r="J47">
-        <v>1.29</v>
+        <v>3.45</v>
       </c>
       <c r="K47">
-        <v>490</v>
+        <v>3.9</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12577,10 +12577,10 @@
         <v>0</v>
       </c>
       <c r="P47">
-        <v>1.24</v>
+        <v>1.83</v>
       </c>
       <c r="Q47">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -12789,7 +12789,7 @@
         <v>294</v>
       </c>
       <c r="F48">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="G48">
         <v>2.1</v>
@@ -12798,13 +12798,13 @@
         <v>3.8</v>
       </c>
       <c r="I48">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J48">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K48">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L48">
         <v>0</v>
@@ -12819,10 +12819,10 @@
         <v>0</v>
       </c>
       <c r="P48">
-        <v>1.24</v>
+        <v>1.88</v>
       </c>
       <c r="Q48">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R48">
         <v>0</v>
@@ -13034,19 +13034,19 @@
         <v>1.4</v>
       </c>
       <c r="G49">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H49">
-        <v>1.14</v>
+        <v>6.8</v>
       </c>
       <c r="I49">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J49">
-        <v>1.14</v>
+        <v>5.5</v>
       </c>
       <c r="K49">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L49">
         <v>0</v>
@@ -13061,10 +13061,10 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q49">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R49">
         <v>0</v>
@@ -13515,19 +13515,19 @@
         <v>297</v>
       </c>
       <c r="F51">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G51">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="H51">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="I51">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J51">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="K51">
         <v>3.55</v>
@@ -13545,7 +13545,7 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q51">
         <v>2.04</v>
@@ -13757,19 +13757,19 @@
         <v>298</v>
       </c>
       <c r="F52">
-        <v>1.35</v>
+        <v>2.58</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>2.96</v>
       </c>
       <c r="H52">
-        <v>1.35</v>
+        <v>2.56</v>
       </c>
       <c r="I52">
-        <v>100</v>
+        <v>2.92</v>
       </c>
       <c r="J52">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K52">
         <v>4</v>
@@ -13787,10 +13787,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q52">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -13799,10 +13799,10 @@
         <v>0</v>
       </c>
       <c r="T52">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U52">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V52">
         <v>0</v>
@@ -13811,112 +13811,112 @@
         <v>0</v>
       </c>
       <c r="X52">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y52">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z52">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA52">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB52">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC52">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD52">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE52">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF52">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG52">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH52">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI52">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ52">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK52">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL52">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM52">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN52">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO52">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP52">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ52">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR52">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS52">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT52">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU52">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV52">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW52">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AX52">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY52">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ52">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA52">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB52">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC52">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD52">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE52">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF52">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG52">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH52">
         <v>0</v>
@@ -13999,28 +13999,28 @@
         <v>299</v>
       </c>
       <c r="F53">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G53">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="H53">
         <v>6.4</v>
       </c>
       <c r="I53">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J53">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="K53">
-        <v>950</v>
+        <v>5.8</v>
       </c>
       <c r="L53">
         <v>0</v>
       </c>
       <c r="M53">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N53">
         <v>0</v>
@@ -14029,10 +14029,10 @@
         <v>0</v>
       </c>
       <c r="P53">
-        <v>1.25</v>
+        <v>2.88</v>
       </c>
       <c r="Q53">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R53">
         <v>0</v>
@@ -14041,10 +14041,10 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="U53">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V53">
         <v>0</v>
@@ -14053,112 +14053,112 @@
         <v>0</v>
       </c>
       <c r="X53">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y53">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z53">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA53">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB53">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC53">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD53">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE53">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF53">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG53">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH53">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI53">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ53">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK53">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL53">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM53">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN53">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AO53">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP53">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AQ53">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="AR53">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS53">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT53">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU53">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV53">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW53">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX53">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY53">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ53">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA53">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB53">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC53">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BD53">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BE53">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF53">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG53">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH53">
         <v>0</v>
@@ -14241,22 +14241,22 @@
         <v>300</v>
       </c>
       <c r="F54">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G54">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="H54">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="I54">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="J54">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="K54">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L54">
         <v>0</v>
@@ -14271,10 +14271,10 @@
         <v>0</v>
       </c>
       <c r="P54">
-        <v>1.12</v>
+        <v>2.9</v>
       </c>
       <c r="Q54">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14486,19 +14486,19 @@
         <v>2.08</v>
       </c>
       <c r="G55">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H55">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="I55">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J55">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="K55">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L55">
         <v>0</v>
@@ -14513,10 +14513,10 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q55">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="R55">
         <v>0</v>
@@ -14725,22 +14725,22 @@
         <v>302</v>
       </c>
       <c r="F56">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="G56">
-        <v>1000</v>
+        <v>2.94</v>
       </c>
       <c r="H56">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I56">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J56">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K56">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L56">
         <v>0</v>
@@ -14755,10 +14755,10 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q56">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -14967,22 +14967,22 @@
         <v>303</v>
       </c>
       <c r="F57">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="G57">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="H57">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="I57">
         <v>1.96</v>
       </c>
       <c r="J57">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="K57">
-        <v>950</v>
+        <v>4.6</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -14991,142 +14991,142 @@
         <v>1.07</v>
       </c>
       <c r="N57">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="O57">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="P57">
-        <v>1.25</v>
+        <v>1.87</v>
       </c>
       <c r="Q57">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="R57">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S57">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T57">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U57">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V57">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="W57">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X57">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y57">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z57">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA57">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB57">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC57">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD57">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE57">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF57">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG57">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH57">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI57">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ57">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK57">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL57">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM57">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN57">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO57">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP57">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ57">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR57">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS57">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT57">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU57">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV57">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW57">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX57">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY57">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AZ57">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA57">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB57">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC57">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD57">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE57">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF57">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG57">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BH57">
         <v>1000</v>
@@ -15212,16 +15212,16 @@
         <v>1.04</v>
       </c>
       <c r="G58">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="H58">
         <v>1.04</v>
       </c>
       <c r="I58">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="J58">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K58">
         <v>950</v>
@@ -15233,22 +15233,22 @@
         <v>1.01</v>
       </c>
       <c r="N58">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="O58">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="P58">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="Q58">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="R58">
         <v>1.25</v>
       </c>
       <c r="S58">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="T58">
         <v>1.01</v>
@@ -15257,10 +15257,10 @@
         <v>1.01</v>
       </c>
       <c r="V58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W58">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X58">
         <v>1000</v>
@@ -15451,22 +15451,22 @@
         <v>305</v>
       </c>
       <c r="F59">
-        <v>1.04</v>
+        <v>1.55</v>
       </c>
       <c r="G59">
-        <v>1000</v>
+        <v>1.65</v>
       </c>
       <c r="H59">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="I59">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J59">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="K59">
-        <v>950</v>
+        <v>5.9</v>
       </c>
       <c r="L59">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>0</v>
       </c>
       <c r="P59">
-        <v>1.25</v>
+        <v>2.72</v>
       </c>
       <c r="Q59">
         <v>1.42</v>
@@ -15693,22 +15693,22 @@
         <v>306</v>
       </c>
       <c r="F60">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="G60">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H60">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="I60">
-        <v>1000</v>
+        <v>1.89</v>
       </c>
       <c r="J60">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="K60">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L60">
         <v>0</v>
@@ -15723,10 +15723,10 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q60">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R60">
         <v>0</v>
@@ -15935,19 +15935,19 @@
         <v>307</v>
       </c>
       <c r="F61">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G61">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H61">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I61">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="J61">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K61">
         <v>950</v>
@@ -15965,10 +15965,10 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>1.24</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R61">
         <v>0</v>
@@ -16177,22 +16177,22 @@
         <v>308</v>
       </c>
       <c r="F62">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G62">
         <v>3.35</v>
       </c>
       <c r="H62">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="I62">
         <v>3.35</v>
       </c>
       <c r="J62">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="K62">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L62">
         <v>0</v>
@@ -16207,10 +16207,10 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q62">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R62">
         <v>0</v>
@@ -16419,22 +16419,22 @@
         <v>309</v>
       </c>
       <c r="F63">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="G63">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H63">
-        <v>1.04</v>
+        <v>2.68</v>
       </c>
       <c r="I63">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J63">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K63">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L63">
         <v>0</v>
@@ -16449,10 +16449,10 @@
         <v>0</v>
       </c>
       <c r="P63">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q63">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R63">
         <v>0</v>
@@ -16661,46 +16661,46 @@
         <v>310</v>
       </c>
       <c r="F64">
+        <v>1.99</v>
+      </c>
+      <c r="G64">
+        <v>2.18</v>
+      </c>
+      <c r="H64">
+        <v>3.3</v>
+      </c>
+      <c r="I64">
+        <v>3.9</v>
+      </c>
+      <c r="J64">
+        <v>3.5</v>
+      </c>
+      <c r="K64">
+        <v>5.2</v>
+      </c>
+      <c r="L64">
         <v>1.25</v>
-      </c>
-      <c r="G64">
-        <v>1000</v>
-      </c>
-      <c r="H64">
-        <v>1.25</v>
-      </c>
-      <c r="I64">
-        <v>1000</v>
-      </c>
-      <c r="J64">
-        <v>1.01</v>
-      </c>
-      <c r="K64">
-        <v>950</v>
-      </c>
-      <c r="L64">
-        <v>1.01</v>
       </c>
       <c r="M64">
         <v>1.01</v>
       </c>
       <c r="N64">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="O64">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P64">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q64">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="R64">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="S64">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="T64">
         <v>1.01</v>
@@ -16709,10 +16709,10 @@
         <v>1.01</v>
       </c>
       <c r="V64">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="W64">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X64">
         <v>1000</v>
@@ -16823,58 +16823,58 @@
         <v>1.01</v>
       </c>
       <c r="BH64">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI64">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ64">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK64">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL64">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM64">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BN64">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO64">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP64">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BQ64">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR64">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS64">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT64">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU64">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV64">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW64">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BX64">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY64">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ64">
         <v>0</v>
@@ -16903,22 +16903,22 @@
         <v>311</v>
       </c>
       <c r="F65">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G65">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="H65">
-        <v>1.27</v>
+        <v>6.8</v>
       </c>
       <c r="I65">
-        <v>100</v>
+        <v>7.8</v>
       </c>
       <c r="J65">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="K65">
-        <v>950</v>
+        <v>5</v>
       </c>
       <c r="L65">
         <v>0</v>
@@ -16933,10 +16933,10 @@
         <v>0</v>
       </c>
       <c r="P65">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q65">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R65">
         <v>0</v>
@@ -16945,10 +16945,10 @@
         <v>0</v>
       </c>
       <c r="T65">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U65">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V65">
         <v>0</v>
@@ -16957,112 +16957,112 @@
         <v>0</v>
       </c>
       <c r="X65">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y65">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z65">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA65">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB65">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC65">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD65">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE65">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF65">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG65">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH65">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI65">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ65">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK65">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL65">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM65">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN65">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO65">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP65">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ65">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AR65">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS65">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT65">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU65">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV65">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AW65">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX65">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY65">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ65">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA65">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BB65">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BC65">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD65">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BE65">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BF65">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG65">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH65">
         <v>0</v>
@@ -17145,22 +17145,22 @@
         <v>312</v>
       </c>
       <c r="F66">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="G66">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="H66">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="I66">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="J66">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="K66">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L66">
         <v>0</v>
@@ -17175,10 +17175,10 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q66">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R66">
         <v>0</v>
@@ -17387,22 +17387,22 @@
         <v>313</v>
       </c>
       <c r="F67">
-        <v>1.42</v>
+        <v>2.34</v>
       </c>
       <c r="G67">
         <v>2.4</v>
       </c>
       <c r="H67">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="I67">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="J67">
-        <v>1.41</v>
+        <v>3.55</v>
       </c>
       <c r="K67">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -17417,10 +17417,10 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="Q67">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -17871,22 +17871,22 @@
         <v>315</v>
       </c>
       <c r="F69">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="G69">
         <v>3.15</v>
       </c>
       <c r="H69">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="I69">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="J69">
-        <v>1.46</v>
+        <v>3.2</v>
       </c>
       <c r="K69">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L69">
         <v>0</v>
@@ -17901,10 +17901,10 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>1.24</v>
+        <v>1.84</v>
       </c>
       <c r="Q69">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -18113,22 +18113,22 @@
         <v>316</v>
       </c>
       <c r="F70">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="G70">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="H70">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="I70">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J70">
-        <v>1.27</v>
+        <v>3.6</v>
       </c>
       <c r="K70">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L70">
         <v>0</v>
@@ -18143,10 +18143,10 @@
         <v>0</v>
       </c>
       <c r="P70">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q70">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R70">
         <v>0</v>
@@ -18355,16 +18355,16 @@
         <v>317</v>
       </c>
       <c r="F71">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="G71">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="H71">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="I71">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J71">
         <v>3.45</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="P71">
-        <v>1.25</v>
+        <v>1.84</v>
       </c>
       <c r="Q71">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R71">
         <v>0</v>
@@ -18597,22 +18597,22 @@
         <v>318</v>
       </c>
       <c r="F72">
-        <v>1.27</v>
+        <v>1.65</v>
       </c>
       <c r="G72">
-        <v>1000</v>
+        <v>1.77</v>
       </c>
       <c r="H72">
-        <v>1.27</v>
+        <v>4.7</v>
       </c>
       <c r="I72">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J72">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="K72">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L72">
         <v>0</v>
@@ -18627,10 +18627,10 @@
         <v>0</v>
       </c>
       <c r="P72">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q72">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R72">
         <v>0</v>
@@ -18639,10 +18639,10 @@
         <v>0</v>
       </c>
       <c r="T72">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="U72">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="V72">
         <v>0</v>
@@ -18651,112 +18651,112 @@
         <v>0</v>
       </c>
       <c r="X72">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y72">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z72">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA72">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB72">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC72">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD72">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE72">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF72">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG72">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH72">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI72">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ72">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK72">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL72">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM72">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN72">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO72">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP72">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AQ72">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR72">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS72">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AT72">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU72">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV72">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW72">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX72">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY72">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ72">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA72">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB72">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC72">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD72">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE72">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF72">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BG72">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH72">
         <v>0</v>
@@ -18839,19 +18839,19 @@
         <v>319</v>
       </c>
       <c r="F73">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="G73">
-        <v>1000</v>
+        <v>2.16</v>
       </c>
       <c r="H73">
-        <v>1.05</v>
+        <v>1.89</v>
       </c>
       <c r="I73">
         <v>1000</v>
       </c>
       <c r="J73">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="K73">
         <v>950</v>
@@ -19081,22 +19081,22 @@
         <v>320</v>
       </c>
       <c r="F74">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="G74">
         <v>1.96</v>
       </c>
       <c r="H74">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I74">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J74">
         <v>3.9</v>
       </c>
       <c r="K74">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L74">
         <v>0</v>
@@ -19111,10 +19111,10 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q74">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="R74">
         <v>0</v>
@@ -19323,10 +19323,10 @@
         <v>321</v>
       </c>
       <c r="F75">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="G75">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="H75">
         <v>1.67</v>
@@ -19335,10 +19335,10 @@
         <v>1.71</v>
       </c>
       <c r="J75">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L75">
         <v>0</v>
@@ -19353,10 +19353,10 @@
         <v>0</v>
       </c>
       <c r="P75">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q75">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="R75">
         <v>0</v>
@@ -19565,7 +19565,7 @@
         <v>322</v>
       </c>
       <c r="F76">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="G76">
         <v>1000</v>
@@ -19577,10 +19577,10 @@
         <v>1000</v>
       </c>
       <c r="J76">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K76">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L76">
         <v>0</v>
@@ -19807,19 +19807,19 @@
         <v>323</v>
       </c>
       <c r="F77">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="G77">
         <v>1000</v>
       </c>
       <c r="H77">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="I77">
         <v>1000</v>
       </c>
       <c r="J77">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="K77">
         <v>7.4</v>
@@ -20049,7 +20049,7 @@
         <v>324</v>
       </c>
       <c r="F78">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="G78">
         <v>1.24</v>
@@ -20058,13 +20058,13 @@
         <v>14</v>
       </c>
       <c r="I78">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="J78">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="K78">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L78">
         <v>0</v>
@@ -20079,10 +20079,10 @@
         <v>0</v>
       </c>
       <c r="P78">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q78">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="R78">
         <v>0</v>
@@ -20094,7 +20094,7 @@
         <v>1.75</v>
       </c>
       <c r="U78">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V78">
         <v>0</v>
@@ -20103,112 +20103,112 @@
         <v>0</v>
       </c>
       <c r="X78">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y78">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z78">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA78">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AB78">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC78">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AD78">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE78">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF78">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG78">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH78">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI78">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ78">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK78">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AL78">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM78">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN78">
-        <v>1000</v>
+        <v>2.6</v>
       </c>
       <c r="AO78">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP78">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ78">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR78">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS78">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AT78">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU78">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AV78">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW78">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX78">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY78">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ78">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA78">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB78">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC78">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD78">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE78">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BF78">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BG78">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH78">
         <v>0</v>
@@ -20291,22 +20291,22 @@
         <v>325</v>
       </c>
       <c r="F79">
-        <v>1.05</v>
+        <v>2.16</v>
       </c>
       <c r="G79">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="H79">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="I79">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J79">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K79">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L79">
         <v>0</v>
@@ -20321,10 +20321,10 @@
         <v>0</v>
       </c>
       <c r="P79">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q79">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R79">
         <v>0</v>
@@ -20775,22 +20775,22 @@
         <v>327</v>
       </c>
       <c r="F81">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="G81">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="H81">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="I81">
-        <v>1000</v>
+        <v>1.88</v>
       </c>
       <c r="J81">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="K81">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -20805,10 +20805,10 @@
         <v>0</v>
       </c>
       <c r="P81">
-        <v>1.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q81">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R81">
         <v>0</v>
@@ -22227,22 +22227,22 @@
         <v>333</v>
       </c>
       <c r="F87">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="G87">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H87">
-        <v>1.32</v>
+        <v>2.2</v>
       </c>
       <c r="I87">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J87">
-        <v>1.3</v>
+        <v>3.3</v>
       </c>
       <c r="K87">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -22257,10 +22257,10 @@
         <v>0</v>
       </c>
       <c r="P87">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q87">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R87">
         <v>0</v>
@@ -22469,22 +22469,22 @@
         <v>334</v>
       </c>
       <c r="F88">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="G88">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H88">
-        <v>1.38</v>
+        <v>2.58</v>
       </c>
       <c r="I88">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="J88">
-        <v>1.55</v>
+        <v>3.25</v>
       </c>
       <c r="K88">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L88">
         <v>0</v>
@@ -22499,10 +22499,10 @@
         <v>0</v>
       </c>
       <c r="P88">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q88">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="R88">
         <v>0</v>
@@ -22711,22 +22711,22 @@
         <v>335</v>
       </c>
       <c r="F89">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="G89">
-        <v>1000</v>
+        <v>1.32</v>
       </c>
       <c r="H89">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="I89">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J89">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="K89">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -22741,10 +22741,10 @@
         <v>0</v>
       </c>
       <c r="P89">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q89">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R89">
         <v>0</v>
@@ -22953,19 +22953,19 @@
         <v>336</v>
       </c>
       <c r="F90">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="G90">
-        <v>1000</v>
+        <v>1.7</v>
       </c>
       <c r="H90">
-        <v>1.25</v>
+        <v>5.1</v>
       </c>
       <c r="I90">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J90">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K90">
         <v>4.9</v>
@@ -22983,10 +22983,10 @@
         <v>0</v>
       </c>
       <c r="P90">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q90">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R90">
         <v>0</v>
@@ -23195,28 +23195,28 @@
         <v>337</v>
       </c>
       <c r="F91">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G91">
-        <v>100</v>
+        <v>1.62</v>
       </c>
       <c r="H91">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I91">
-        <v>100</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J91">
-        <v>1.02</v>
+        <v>4.4</v>
       </c>
       <c r="K91">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L91">
         <v>0</v>
       </c>
       <c r="M91">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N91">
         <v>0</v>
@@ -23225,10 +23225,10 @@
         <v>0</v>
       </c>
       <c r="P91">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q91">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R91">
         <v>0</v>
@@ -23237,10 +23237,10 @@
         <v>0</v>
       </c>
       <c r="T91">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U91">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V91">
         <v>0</v>
@@ -23249,112 +23249,112 @@
         <v>0</v>
       </c>
       <c r="X91">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y91">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z91">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA91">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB91">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC91">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD91">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE91">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF91">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG91">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH91">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI91">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ91">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK91">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL91">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM91">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN91">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO91">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP91">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ91">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR91">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS91">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT91">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU91">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV91">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW91">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX91">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AY91">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ91">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA91">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB91">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC91">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD91">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE91">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF91">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG91">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH91">
         <v>0</v>
@@ -23679,22 +23679,22 @@
         <v>339</v>
       </c>
       <c r="F93">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G93">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H93">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="I93">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="J93">
-        <v>1.65</v>
+        <v>3.7</v>
       </c>
       <c r="K93">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="L93">
         <v>0</v>
@@ -23709,7 +23709,7 @@
         <v>0</v>
       </c>
       <c r="P93">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q93">
         <v>1.68</v>
@@ -23921,22 +23921,22 @@
         <v>340</v>
       </c>
       <c r="F94">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="G94">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H94">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="I94">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J94">
-        <v>1.16</v>
+        <v>3.95</v>
       </c>
       <c r="K94">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -23951,10 +23951,10 @@
         <v>0</v>
       </c>
       <c r="P94">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q94">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -24435,7 +24435,7 @@
         <v>0</v>
       </c>
       <c r="P96">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q96">
         <v>1.01</v>
@@ -24647,22 +24647,22 @@
         <v>343</v>
       </c>
       <c r="F97">
-        <v>1.35</v>
+        <v>2.34</v>
       </c>
       <c r="G97">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="H97">
-        <v>1.6</v>
+        <v>2.94</v>
       </c>
       <c r="I97">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="J97">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="K97">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L97">
         <v>0</v>
@@ -24677,10 +24677,10 @@
         <v>0</v>
       </c>
       <c r="P97">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q97">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R97">
         <v>0</v>
@@ -24889,22 +24889,22 @@
         <v>344</v>
       </c>
       <c r="F98">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="G98">
         <v>1.53</v>
       </c>
       <c r="H98">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I98">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="J98">
         <v>4.8</v>
       </c>
       <c r="K98">
-        <v>950</v>
+        <v>5.7</v>
       </c>
       <c r="L98">
         <v>0</v>
@@ -24919,10 +24919,10 @@
         <v>0</v>
       </c>
       <c r="P98">
-        <v>1.25</v>
+        <v>2.64</v>
       </c>
       <c r="Q98">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="R98">
         <v>0</v>
@@ -24943,112 +24943,112 @@
         <v>0</v>
       </c>
       <c r="X98">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y98">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z98">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA98">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB98">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC98">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD98">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE98">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF98">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG98">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH98">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI98">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ98">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK98">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL98">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM98">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN98">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO98">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP98">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ98">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR98">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS98">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT98">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU98">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AV98">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AW98">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX98">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY98">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ98">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA98">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB98">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC98">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BD98">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE98">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF98">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG98">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH98">
         <v>0</v>
@@ -25373,22 +25373,22 @@
         <v>346</v>
       </c>
       <c r="F100">
-        <v>1.06</v>
+        <v>14.5</v>
       </c>
       <c r="G100">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="H100">
-        <v>1.06</v>
+        <v>1.23</v>
       </c>
       <c r="I100">
-        <v>1000</v>
+        <v>1.29</v>
       </c>
       <c r="J100">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="K100">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="L100">
         <v>0</v>
@@ -25403,10 +25403,10 @@
         <v>0</v>
       </c>
       <c r="P100">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q100">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -25630,7 +25630,7 @@
         <v>1.01</v>
       </c>
       <c r="K101">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="L101">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-08.xlsx
@@ -1777,7 +1777,7 @@
     <t>Houston Dynamo</t>
   </si>
   <si>
-    <t>2026-08-06 19:37:28</t>
+    <t>2026-08-06 21:58:41</t>
   </si>
 </sst>
 </file>
@@ -2371,19 +2371,19 @@
         <v>387</v>
       </c>
       <c r="F2">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G2">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H2">
         <v>2.66</v>
       </c>
       <c r="I2">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="J2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
         <v>3.7</v>
@@ -2395,13 +2395,13 @@
         <v>1.07</v>
       </c>
       <c r="N2">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O2">
         <v>1.34</v>
       </c>
       <c r="P2">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q2">
         <v>2</v>
@@ -2413,7 +2413,7 @@
         <v>3.5</v>
       </c>
       <c r="T2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U2">
         <v>2.08</v>
@@ -2422,7 +2422,7 @@
         <v>1.55</v>
       </c>
       <c r="W2">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X2">
         <v>15</v>
@@ -2431,7 +2431,7 @@
         <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA2">
         <v>48</v>
@@ -2449,7 +2449,7 @@
         <v>34</v>
       </c>
       <c r="AF2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG2">
         <v>13.5</v>
@@ -2482,55 +2482,55 @@
         <v>10</v>
       </c>
       <c r="AQ2">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
         <v>14</v>
       </c>
       <c r="AS2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT2">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AU2">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AV2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX2">
         <v>14</v>
       </c>
       <c r="AY2">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
         <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BG2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH2">
         <v>3.4</v>
@@ -2613,22 +2613,22 @@
         <v>388</v>
       </c>
       <c r="F3">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="G3">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I3">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
         <v>3.15</v>
       </c>
       <c r="K3">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -2637,13 +2637,13 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="O3">
         <v>1.36</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
         <v>2.08</v>
@@ -2655,16 +2655,16 @@
         <v>3</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U3">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2855,7 +2855,7 @@
         <v>389</v>
       </c>
       <c r="F4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="G4">
         <v>1.38</v>
@@ -2885,16 +2885,16 @@
         <v>1.14</v>
       </c>
       <c r="P4">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="Q4">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R4">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S4">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="T4">
         <v>1.82</v>
@@ -2903,7 +2903,7 @@
         <v>2.04</v>
       </c>
       <c r="V4">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W4">
         <v>3.6</v>
@@ -2921,7 +2921,7 @@
         <v>330</v>
       </c>
       <c r="AB4">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC4">
         <v>16.5</v>
@@ -2963,16 +2963,16 @@
         <v>140</v>
       </c>
       <c r="AP4">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ4">
         <v>29</v>
       </c>
       <c r="AR4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS4">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT4">
         <v>10.5</v>
@@ -2984,7 +2984,7 @@
         <v>26</v>
       </c>
       <c r="AW4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
         <v>9</v>
@@ -2996,7 +2996,7 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB4">
         <v>10</v>
@@ -3005,16 +3005,16 @@
         <v>12</v>
       </c>
       <c r="BD4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
         <v>3.5</v>
       </c>
       <c r="BG4">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -3097,22 +3097,22 @@
         <v>390</v>
       </c>
       <c r="F5">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="G5">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="H5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="K5">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -3121,22 +3121,22 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="O5">
         <v>1.58</v>
       </c>
       <c r="P5">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Q5">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="R5">
         <v>1.13</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -3145,10 +3145,10 @@
         <v>1.11</v>
       </c>
       <c r="V5">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="W5">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -3342,7 +3342,7 @@
         <v>1.51</v>
       </c>
       <c r="G6">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -3584,7 +3584,7 @@
         <v>1.82</v>
       </c>
       <c r="G7">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H7">
         <v>4.3</v>
@@ -3617,130 +3617,130 @@
         <v>1.89</v>
       </c>
       <c r="R7">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7">
         <v>3.25</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
         <v>1.24</v>
       </c>
       <c r="W7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH7">
         <v>4.1</v>
@@ -3823,19 +3823,19 @@
         <v>393</v>
       </c>
       <c r="F8">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="G8">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I8">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K8">
         <v>3.7</v>
@@ -3853,10 +3853,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q8">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -4101,7 +4101,7 @@
         <v>2.12</v>
       </c>
       <c r="R9">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S9">
         <v>3.75</v>
@@ -4573,19 +4573,19 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P11">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="Q11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R11">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="S11">
         <v>1.25</v>
@@ -4815,13 +4815,13 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O12">
         <v>1.31</v>
       </c>
       <c r="P12">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q12">
         <v>1.31</v>
@@ -5275,10 +5275,10 @@
         <v>399</v>
       </c>
       <c r="F14">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="G14">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H14">
         <v>1.05</v>
@@ -5287,7 +5287,7 @@
         <v>1.93</v>
       </c>
       <c r="J14">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -5299,7 +5299,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O14">
         <v>1.34</v>
@@ -6294,7 +6294,7 @@
         <v>1.2</v>
       </c>
       <c r="W18">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -6488,7 +6488,7 @@
         <v>4.1</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H19">
         <v>2.04</v>
@@ -6730,7 +6730,7 @@
         <v>1.9</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H20">
         <v>4.2</v>
@@ -7232,31 +7232,31 @@
         <v>1.35</v>
       </c>
       <c r="M22">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O22">
         <v>1.27</v>
       </c>
       <c r="P22">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q22">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="R22">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S22">
         <v>3.1</v>
       </c>
       <c r="T22">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U22">
-        <v>1.89</v>
+        <v>1.12</v>
       </c>
       <c r="V22">
         <v>1.35</v>
@@ -7504,7 +7504,7 @@
         <v>1.41</v>
       </c>
       <c r="W23">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X23">
         <v>12</v>
@@ -7701,7 +7701,7 @@
         <v>5</v>
       </c>
       <c r="H24">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I24">
         <v>2.14</v>
@@ -7710,7 +7710,7 @@
         <v>3.1</v>
       </c>
       <c r="K24">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L24">
         <v>1.54</v>
@@ -7746,10 +7746,10 @@
         <v>1.9</v>
       </c>
       <c r="W24">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X24">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>7.6</v>
@@ -7764,7 +7764,7 @@
         <v>14</v>
       </c>
       <c r="AC24">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD24">
         <v>13.5</v>
@@ -7827,31 +7827,31 @@
         <v>21</v>
       </c>
       <c r="AX24">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY24">
         <v>15.5</v>
       </c>
       <c r="AZ24">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BA24">
+        <v>5.5</v>
+      </c>
+      <c r="BB24">
         <v>5.7</v>
       </c>
-      <c r="BB24">
-        <v>5.9</v>
-      </c>
       <c r="BC24">
+        <v>5.6</v>
+      </c>
+      <c r="BD24">
+        <v>5.7</v>
+      </c>
+      <c r="BE24">
         <v>5.8</v>
       </c>
-      <c r="BD24">
-        <v>5.9</v>
-      </c>
-      <c r="BE24">
-        <v>6</v>
-      </c>
       <c r="BF24">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG24">
         <v>19.5</v>
@@ -7937,7 +7937,7 @@
         <v>410</v>
       </c>
       <c r="F25">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G25">
         <v>1.69</v>
@@ -7970,7 +7970,7 @@
         <v>1.89</v>
       </c>
       <c r="Q25">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R25">
         <v>1.34</v>
@@ -8042,7 +8042,7 @@
         <v>12.5</v>
       </c>
       <c r="AO25">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP25">
         <v>10.5</v>
@@ -8185,7 +8185,7 @@
         <v>1.55</v>
       </c>
       <c r="H26">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I26">
         <v>9.199999999999999</v>
@@ -8200,25 +8200,25 @@
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N26">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O26">
         <v>1.27</v>
       </c>
       <c r="P26">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="Q26">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R26">
         <v>1.37</v>
       </c>
       <c r="S26">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -8905,19 +8905,19 @@
         <v>414</v>
       </c>
       <c r="F29">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G29">
         <v>3.1</v>
       </c>
       <c r="H29">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I29">
         <v>2.74</v>
       </c>
       <c r="J29">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K29">
         <v>3.6</v>
@@ -8929,34 +8929,34 @@
         <v>1.07</v>
       </c>
       <c r="N29">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="O29">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P29">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q29">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R29">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="S29">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T29">
         <v>1.77</v>
       </c>
       <c r="U29">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V29">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W29">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X29">
         <v>17</v>
@@ -8965,7 +8965,7 @@
         <v>13</v>
       </c>
       <c r="Z29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA29">
         <v>48</v>
@@ -9016,13 +9016,13 @@
         <v>12</v>
       </c>
       <c r="AQ29">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR29">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AS29">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AT29">
         <v>10</v>
@@ -9046,22 +9046,22 @@
         <v>15</v>
       </c>
       <c r="BA29">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BB29">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BC29">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD29">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BE29">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF29">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BG29">
         <v>17.5</v>
@@ -9150,16 +9150,16 @@
         <v>4</v>
       </c>
       <c r="G30">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I30">
         <v>2.08</v>
       </c>
       <c r="J30">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K30">
         <v>3.8</v>
@@ -9177,10 +9177,10 @@
         <v>1.3</v>
       </c>
       <c r="P30">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q30">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R30">
         <v>1.4</v>
@@ -9189,19 +9189,19 @@
         <v>3.25</v>
       </c>
       <c r="T30">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U30">
         <v>2.18</v>
       </c>
       <c r="V30">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W30">
         <v>1.31</v>
       </c>
       <c r="X30">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y30">
         <v>11.5</v>
@@ -9213,10 +9213,10 @@
         <v>27</v>
       </c>
       <c r="AB30">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC30">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD30">
         <v>12.5</v>
@@ -9276,34 +9276,34 @@
         <v>9.4</v>
       </c>
       <c r="AW30">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="AX30">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY30">
         <v>14.5</v>
       </c>
       <c r="AZ30">
-        <v>5</v>
+        <v>15.5</v>
       </c>
       <c r="BA30">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB30">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC30">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD30">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE30">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF30">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG30">
         <v>11.5</v>
@@ -9318,19 +9318,19 @@
         <v>9.6</v>
       </c>
       <c r="BK30">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL30">
         <v>1000</v>
       </c>
       <c r="BM30">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN30">
         <v>7.6</v>
       </c>
       <c r="BO30">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BP30">
         <v>34</v>
@@ -9342,7 +9342,7 @@
         <v>1000</v>
       </c>
       <c r="BS30">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT30">
         <v>4.8</v>
@@ -9354,16 +9354,16 @@
         <v>14</v>
       </c>
       <c r="BW30">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX30">
         <v>27</v>
       </c>
       <c r="BY30">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ30">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA30">
         <v>9.199999999999999</v>
@@ -9389,19 +9389,19 @@
         <v>416</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G31">
         <v>2.1</v>
       </c>
       <c r="H31">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I31">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J31">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K31">
         <v>3.5</v>
@@ -9413,7 +9413,7 @@
         <v>1.1</v>
       </c>
       <c r="N31">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O31">
         <v>1.45</v>
@@ -9422,16 +9422,16 @@
         <v>1.64</v>
       </c>
       <c r="Q31">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R31">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S31">
         <v>4.6</v>
       </c>
       <c r="T31">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U31">
         <v>1.87</v>
@@ -9440,7 +9440,7 @@
         <v>1.25</v>
       </c>
       <c r="W31">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X31">
         <v>12</v>
@@ -9458,7 +9458,7 @@
         <v>7.8</v>
       </c>
       <c r="AC31">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD31">
         <v>19.5</v>
@@ -9491,19 +9491,19 @@
         <v>180</v>
       </c>
       <c r="AN31">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO31">
         <v>120</v>
       </c>
       <c r="AP31">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ31">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR31">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AS31">
         <v>6.2</v>
@@ -9515,22 +9515,22 @@
         <v>6.8</v>
       </c>
       <c r="AV31">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW31">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AX31">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY31">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ31">
         <v>18.5</v>
       </c>
       <c r="BA31">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB31">
         <v>19.5</v>
@@ -9539,19 +9539,19 @@
         <v>19.5</v>
       </c>
       <c r="BD31">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE31">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF31">
         <v>18</v>
       </c>
       <c r="BG31">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BH31">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI31">
         <v>2.44</v>
@@ -9560,55 +9560,55 @@
         <v>12.5</v>
       </c>
       <c r="BK31">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BN31">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BO31">
         <v>3.65</v>
       </c>
       <c r="BP31">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BQ31">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BR31">
         <v>42</v>
       </c>
       <c r="BS31">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BT31">
         <v>8.800000000000001</v>
       </c>
       <c r="BU31">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BV31">
         <v>55</v>
       </c>
       <c r="BW31">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BX31">
         <v>1000</v>
       </c>
       <c r="BY31">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BZ31">
         <v>42</v>
       </c>
       <c r="CA31">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="CB31" t="s">
         <v>587</v>
@@ -9634,19 +9634,19 @@
         <v>1.76</v>
       </c>
       <c r="G32">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="H32">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I32">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -9655,34 +9655,34 @@
         <v>1.08</v>
       </c>
       <c r="N32">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O32">
         <v>1.35</v>
       </c>
       <c r="P32">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Q32">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R32">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S32">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T32">
+        <v>1.98</v>
+      </c>
+      <c r="U32">
         <v>1.95</v>
-      </c>
-      <c r="U32">
-        <v>1.79</v>
       </c>
       <c r="V32">
         <v>1.2</v>
       </c>
       <c r="W32">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X32">
         <v>16.5</v>
@@ -9697,13 +9697,13 @@
         <v>170</v>
       </c>
       <c r="AB32">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC32">
         <v>10.5</v>
       </c>
       <c r="AD32">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE32">
         <v>95</v>
@@ -9724,7 +9724,7 @@
         <v>23</v>
       </c>
       <c r="AK32">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL32">
         <v>48</v>
@@ -9733,64 +9733,64 @@
         <v>160</v>
       </c>
       <c r="AN32">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO32">
         <v>120</v>
       </c>
       <c r="AP32">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ32">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR32">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS32">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT32">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU32">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV32">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW32">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX32">
+        <v>9.4</v>
+      </c>
+      <c r="AY32">
         <v>9</v>
-      </c>
-      <c r="AY32">
-        <v>8.800000000000001</v>
       </c>
       <c r="AZ32">
         <v>18</v>
       </c>
       <c r="BA32">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB32">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC32">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD32">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE32">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF32">
         <v>11</v>
       </c>
       <c r="BG32">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -10118,28 +10118,28 @@
         <v>2.74</v>
       </c>
       <c r="G34">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H34">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I34">
         <v>2.96</v>
       </c>
       <c r="J34">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K34">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L34">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M34">
         <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O34">
         <v>1.34</v>
@@ -10196,7 +10196,7 @@
         <v>21</v>
       </c>
       <c r="AG34">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH34">
         <v>19.5</v>
@@ -10208,7 +10208,7 @@
         <v>55</v>
       </c>
       <c r="AK34">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL34">
         <v>55</v>
@@ -10220,7 +10220,7 @@
         <v>36</v>
       </c>
       <c r="AO34">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AP34">
         <v>11.5</v>
@@ -10244,7 +10244,7 @@
         <v>11</v>
       </c>
       <c r="AW34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX34">
         <v>16</v>
@@ -10256,19 +10256,19 @@
         <v>15</v>
       </c>
       <c r="BA34">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB34">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BC34">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD34">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE34">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF34">
         <v>21</v>
@@ -10387,7 +10387,7 @@
         <v>1.24</v>
       </c>
       <c r="P35">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q35">
         <v>1.71</v>
@@ -10405,7 +10405,7 @@
         <v>2.32</v>
       </c>
       <c r="V35">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W35">
         <v>1.75</v>
@@ -10519,7 +10519,7 @@
         <v>4.6</v>
       </c>
       <c r="BH35">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI35">
         <v>3.2</v>
@@ -10528,7 +10528,7 @@
         <v>10.5</v>
       </c>
       <c r="BK35">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BL35">
         <v>110</v>
@@ -10552,10 +10552,10 @@
         <v>29</v>
       </c>
       <c r="BS35">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BT35">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU35">
         <v>5.4</v>
@@ -10564,13 +10564,13 @@
         <v>29</v>
       </c>
       <c r="BW35">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BX35">
         <v>38</v>
       </c>
       <c r="BY35">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BZ35">
         <v>0</v>
@@ -10602,13 +10602,13 @@
         <v>4.4</v>
       </c>
       <c r="G36">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H36">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I36">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="J36">
         <v>4.4</v>
@@ -10647,10 +10647,10 @@
         <v>2.5</v>
       </c>
       <c r="V36">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="W36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X36">
         <v>36</v>
@@ -10844,13 +10844,13 @@
         <v>2.68</v>
       </c>
       <c r="G37">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H37">
         <v>2.48</v>
       </c>
       <c r="I37">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J37">
         <v>3.9</v>
@@ -11083,10 +11083,10 @@
         <v>423</v>
       </c>
       <c r="F38">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="G38">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H38">
         <v>4.3</v>
@@ -11113,13 +11113,13 @@
         <v>1.24</v>
       </c>
       <c r="P38">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q38">
         <v>1.67</v>
       </c>
       <c r="R38">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S38">
         <v>2.72</v>
@@ -11325,16 +11325,16 @@
         <v>424</v>
       </c>
       <c r="F39">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G39">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H39">
         <v>3.05</v>
       </c>
       <c r="I39">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J39">
         <v>3.8</v>
@@ -11349,7 +11349,7 @@
         <v>1.04</v>
       </c>
       <c r="N39">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O39">
         <v>1.21</v>
@@ -11370,10 +11370,10 @@
         <v>1.55</v>
       </c>
       <c r="U39">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V39">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W39">
         <v>1.71</v>
@@ -11597,7 +11597,7 @@
         <v>1.23</v>
       </c>
       <c r="P40">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q40">
         <v>1.7</v>
@@ -11621,7 +11621,7 @@
         <v>2.38</v>
       </c>
       <c r="X40">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y40">
         <v>25</v>
@@ -11657,7 +11657,7 @@
         <v>70</v>
       </c>
       <c r="AJ40">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK40">
         <v>16.5</v>
@@ -11666,7 +11666,7 @@
         <v>34</v>
       </c>
       <c r="AM40">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN40">
         <v>9</v>
@@ -11684,7 +11684,7 @@
         <v>40</v>
       </c>
       <c r="AS40">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT40">
         <v>9.6</v>
@@ -11699,7 +11699,7 @@
         <v>55</v>
       </c>
       <c r="AX40">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY40">
         <v>9.199999999999999</v>
@@ -11720,7 +11720,7 @@
         <v>26</v>
       </c>
       <c r="BE40">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF40">
         <v>7.4</v>
@@ -11821,7 +11821,7 @@
         <v>990</v>
       </c>
       <c r="J41">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K41">
         <v>500</v>
@@ -11848,7 +11848,7 @@
         <v>1.18</v>
       </c>
       <c r="S41">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
         <v>1.11</v>
@@ -12535,13 +12535,13 @@
         <v>429</v>
       </c>
       <c r="F44">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="G44">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H44">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I44">
         <v>3.15</v>
@@ -12565,10 +12565,10 @@
         <v>1.27</v>
       </c>
       <c r="P44">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q44">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="R44">
         <v>1.33</v>
@@ -12580,13 +12580,13 @@
         <v>1.54</v>
       </c>
       <c r="U44">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V44">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W44">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X44">
         <v>1000</v>
@@ -13503,10 +13503,10 @@
         <v>433</v>
       </c>
       <c r="F48">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="G48">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H48">
         <v>4.3</v>
@@ -13518,7 +13518,7 @@
         <v>4.4</v>
       </c>
       <c r="K48">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -13539,10 +13539,10 @@
         <v>1.4</v>
       </c>
       <c r="R48">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="S48">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="T48">
         <v>1.53</v>
@@ -13554,7 +13554,7 @@
         <v>1.25</v>
       </c>
       <c r="W48">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X48">
         <v>38</v>
@@ -13641,7 +13641,7 @@
         <v>8</v>
       </c>
       <c r="AZ48">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA48">
         <v>5</v>
@@ -13745,28 +13745,28 @@
         <v>434</v>
       </c>
       <c r="F49">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G49">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H49">
         <v>4.9</v>
       </c>
       <c r="I49">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J49">
         <v>4.4</v>
       </c>
       <c r="K49">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L49">
         <v>1.01</v>
       </c>
       <c r="M49">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N49">
         <v>5.8</v>
@@ -13778,13 +13778,13 @@
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R49">
         <v>1.64</v>
       </c>
       <c r="S49">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T49">
         <v>1.6</v>
@@ -13796,13 +13796,13 @@
         <v>1.22</v>
       </c>
       <c r="W49">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X49">
         <v>32</v>
       </c>
       <c r="Y49">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z49">
         <v>55</v>
@@ -13820,7 +13820,7 @@
         <v>24</v>
       </c>
       <c r="AE49">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF49">
         <v>13</v>
@@ -13850,7 +13850,7 @@
         <v>6.6</v>
       </c>
       <c r="AO49">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP49">
         <v>20</v>
@@ -13862,7 +13862,7 @@
         <v>34</v>
       </c>
       <c r="AS49">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT49">
         <v>11</v>
@@ -13874,7 +13874,7 @@
         <v>17.5</v>
       </c>
       <c r="AW49">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX49">
         <v>10.5</v>
@@ -13886,7 +13886,7 @@
         <v>15.5</v>
       </c>
       <c r="BA49">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB49">
         <v>15.5</v>
@@ -13898,13 +13898,13 @@
         <v>21</v>
       </c>
       <c r="BE49">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF49">
         <v>5.8</v>
       </c>
       <c r="BG49">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -14020,7 +14020,7 @@
         <v>1.25</v>
       </c>
       <c r="Q50">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="R50">
         <v>1.18</v>
@@ -14238,7 +14238,7 @@
         <v>1.98</v>
       </c>
       <c r="I51">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J51">
         <v>4.1</v>
@@ -14256,7 +14256,7 @@
         <v>7</v>
       </c>
       <c r="O51">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P51">
         <v>3</v>
@@ -14265,19 +14265,19 @@
         <v>1.41</v>
       </c>
       <c r="R51">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="S51">
         <v>2</v>
       </c>
       <c r="T51">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="U51">
         <v>2.66</v>
       </c>
       <c r="V51">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W51">
         <v>1.38</v>
@@ -14471,7 +14471,7 @@
         <v>437</v>
       </c>
       <c r="F52">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G52">
         <v>2.96</v>
@@ -14504,7 +14504,7 @@
         <v>2.1</v>
       </c>
       <c r="Q52">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R52">
         <v>1.43</v>
@@ -14746,7 +14746,7 @@
         <v>2.38</v>
       </c>
       <c r="Q53">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R53">
         <v>1.56</v>
@@ -14755,7 +14755,7 @@
         <v>2.44</v>
       </c>
       <c r="T53">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="U53">
         <v>2.48</v>
@@ -14827,7 +14827,7 @@
         <v>12.5</v>
       </c>
       <c r="AR53">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS53">
         <v>4.5</v>
@@ -14967,7 +14967,7 @@
         <v>1.53</v>
       </c>
       <c r="J54">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="K54">
         <v>5.5</v>
@@ -14985,7 +14985,7 @@
         <v>1.12</v>
       </c>
       <c r="P54">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q54">
         <v>1.37</v>
@@ -14994,19 +14994,19 @@
         <v>1.98</v>
       </c>
       <c r="S54">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="T54">
         <v>1.54</v>
       </c>
       <c r="U54">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="V54">
         <v>2.88</v>
       </c>
       <c r="W54">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X54">
         <v>42</v>
@@ -15015,7 +15015,7 @@
         <v>17</v>
       </c>
       <c r="Z54">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA54">
         <v>16.5</v>
@@ -15030,7 +15030,7 @@
         <v>11.5</v>
       </c>
       <c r="AE54">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF54">
         <v>65</v>
@@ -15063,7 +15063,7 @@
         <v>4.4</v>
       </c>
       <c r="AP54">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AQ54">
         <v>15</v>
@@ -15099,7 +15099,7 @@
         <v>19.5</v>
       </c>
       <c r="BB54">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="BC54">
         <v>50</v>
@@ -15111,10 +15111,10 @@
         <v>46</v>
       </c>
       <c r="BF54">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG54">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -15206,7 +15206,7 @@
         <v>6</v>
       </c>
       <c r="I55">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J55">
         <v>4.6</v>
@@ -15218,10 +15218,10 @@
         <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N55">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="O55">
         <v>1.18</v>
@@ -15230,19 +15230,19 @@
         <v>2.66</v>
       </c>
       <c r="Q55">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R55">
         <v>1.69</v>
       </c>
       <c r="S55">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="T55">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U55">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V55">
         <v>1.16</v>
@@ -15251,7 +15251,7 @@
         <v>2.64</v>
       </c>
       <c r="X55">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y55">
         <v>32</v>
@@ -15260,34 +15260,34 @@
         <v>60</v>
       </c>
       <c r="AA55">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB55">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC55">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD55">
         <v>26</v>
       </c>
       <c r="AE55">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF55">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG55">
         <v>10.5</v>
       </c>
       <c r="AH55">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI55">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ55">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AK55">
         <v>15</v>
@@ -15314,7 +15314,7 @@
         <v>46</v>
       </c>
       <c r="AS55">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT55">
         <v>10.5</v>
@@ -15347,16 +15347,16 @@
         <v>12.5</v>
       </c>
       <c r="BD55">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE55">
-        <v>60</v>
+        <v>10.5</v>
       </c>
       <c r="BF55">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BG55">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BH55">
         <v>6.2</v>
@@ -15368,13 +15368,13 @@
         <v>13</v>
       </c>
       <c r="BK55">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BL55">
         <v>1000</v>
       </c>
       <c r="BM55">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BN55">
         <v>6</v>
@@ -15386,25 +15386,25 @@
         <v>13</v>
       </c>
       <c r="BQ55">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="BR55">
         <v>28</v>
       </c>
       <c r="BS55">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BT55">
         <v>13.5</v>
       </c>
       <c r="BU55">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BV55">
         <v>1000</v>
       </c>
       <c r="BW55">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BX55">
         <v>1000</v>
@@ -15413,7 +15413,7 @@
         <v>3</v>
       </c>
       <c r="BZ55">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CA55">
         <v>2.68</v>
@@ -15469,13 +15469,13 @@
         <v>1.22</v>
       </c>
       <c r="P56">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q56">
         <v>1.62</v>
       </c>
       <c r="R56">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S56">
         <v>2.44</v>
@@ -15711,13 +15711,13 @@
         <v>1.12</v>
       </c>
       <c r="P57">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q57">
         <v>1.38</v>
       </c>
       <c r="R57">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S57">
         <v>2</v>
@@ -15756,7 +15756,7 @@
         <v>14.5</v>
       </c>
       <c r="AE57">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF57">
         <v>34</v>
@@ -15780,16 +15780,16 @@
         <v>32</v>
       </c>
       <c r="AM57">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN57">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO57">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AP57">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AQ57">
         <v>16</v>
@@ -15798,7 +15798,7 @@
         <v>16.5</v>
       </c>
       <c r="AS57">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AT57">
         <v>20</v>
@@ -15813,7 +15813,7 @@
         <v>15.5</v>
       </c>
       <c r="AX57">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY57">
         <v>13</v>
@@ -15825,16 +15825,16 @@
         <v>19.5</v>
       </c>
       <c r="BB57">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC57">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD57">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE57">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF57">
         <v>13.5</v>
@@ -15935,7 +15935,7 @@
         <v>4.9</v>
       </c>
       <c r="J58">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K58">
         <v>4.8</v>
@@ -15947,7 +15947,7 @@
         <v>1.03</v>
       </c>
       <c r="N58">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O58">
         <v>1.19</v>
@@ -15962,10 +15962,10 @@
         <v>1.6</v>
       </c>
       <c r="S58">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T58">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U58">
         <v>2.4</v>
@@ -16407,19 +16407,19 @@
         <v>445</v>
       </c>
       <c r="F60">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="G60">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="H60">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I60">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J60">
-        <v>2.58</v>
+        <v>2.98</v>
       </c>
       <c r="K60">
         <v>4.4</v>
@@ -16428,37 +16428,37 @@
         <v>1.34</v>
       </c>
       <c r="M60">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N60">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O60">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="P60">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="Q60">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R60">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="S60">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="T60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V60">
         <v>1.35</v>
       </c>
       <c r="W60">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -16897,16 +16897,16 @@
         <v>110</v>
       </c>
       <c r="H62">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="I62">
-        <v>3.95</v>
+        <v>21</v>
       </c>
       <c r="J62">
-        <v>2.88</v>
+        <v>1.05</v>
       </c>
       <c r="K62">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L62">
         <v>1.01</v>
@@ -16915,13 +16915,13 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O62">
         <v>1.38</v>
       </c>
       <c r="P62">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q62">
         <v>1.38</v>
@@ -16930,7 +16930,7 @@
         <v>1.18</v>
       </c>
       <c r="S62">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="T62">
         <v>1.01</v>
@@ -16939,7 +16939,7 @@
         <v>1.01</v>
       </c>
       <c r="V62">
-        <v>1.61</v>
+        <v>1.05</v>
       </c>
       <c r="W62">
         <v>1.02</v>
@@ -16948,7 +16948,7 @@
         <v>44</v>
       </c>
       <c r="Y62">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z62">
         <v>20</v>
@@ -16957,64 +16957,64 @@
         <v>30</v>
       </c>
       <c r="AB62">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AC62">
         <v>15.5</v>
       </c>
       <c r="AD62">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE62">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF62">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AG62">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AH62">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AI62">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AJ62">
+        <v>720</v>
+      </c>
+      <c r="AK62">
+        <v>490</v>
+      </c>
+      <c r="AL62">
+        <v>650</v>
+      </c>
+      <c r="AM62">
         <v>990</v>
       </c>
-      <c r="AK62">
-        <v>800</v>
-      </c>
-      <c r="AL62">
-        <v>990</v>
-      </c>
-      <c r="AM62">
-        <v>1000</v>
-      </c>
       <c r="AN62">
         <v>1000</v>
       </c>
       <c r="AO62">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AP62">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ62">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="AR62">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS62">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT62">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU62">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV62">
         <v>8.4</v>
@@ -17023,7 +17023,7 @@
         <v>10.5</v>
       </c>
       <c r="AX62">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AY62">
         <v>14.5</v>
@@ -17035,7 +17035,7 @@
         <v>17</v>
       </c>
       <c r="BB62">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="BC62">
         <v>30</v>
@@ -17044,13 +17044,13 @@
         <v>27</v>
       </c>
       <c r="BE62">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF62">
         <v>15</v>
       </c>
       <c r="BG62">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -17868,7 +17868,7 @@
         <v>2.72</v>
       </c>
       <c r="I66">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J66">
         <v>3.95</v>
@@ -17883,7 +17883,7 @@
         <v>1.01</v>
       </c>
       <c r="N66">
-        <v>4.6</v>
+        <v>2.56</v>
       </c>
       <c r="O66">
         <v>1.16</v>
@@ -17901,13 +17901,13 @@
         <v>2.18</v>
       </c>
       <c r="T66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V66">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W66">
         <v>1.63</v>
@@ -18367,7 +18367,7 @@
         <v>1.01</v>
       </c>
       <c r="N68">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O68">
         <v>1.13</v>
@@ -19099,10 +19099,10 @@
         <v>1.15</v>
       </c>
       <c r="P71">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="Q71">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="R71">
         <v>1.56</v>
@@ -19401,7 +19401,7 @@
         <v>90</v>
       </c>
       <c r="AJ72">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK72">
         <v>19</v>
@@ -19425,13 +19425,13 @@
         <v>14.5</v>
       </c>
       <c r="AR72">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AS72">
         <v>1.01</v>
       </c>
       <c r="AT72">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU72">
         <v>7.2</v>
@@ -19443,10 +19443,10 @@
         <v>1.01</v>
       </c>
       <c r="AX72">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY72">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AZ72">
         <v>16</v>
@@ -19458,10 +19458,10 @@
         <v>1.01</v>
       </c>
       <c r="BC72">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD72">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BE72">
         <v>1.01</v>
@@ -19795,13 +19795,13 @@
         <v>459</v>
       </c>
       <c r="F74">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="G74">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H74">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="I74">
         <v>2.02</v>
@@ -19810,16 +19810,16 @@
         <v>3.75</v>
       </c>
       <c r="K74">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L74">
         <v>1.28</v>
       </c>
       <c r="M74">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N74">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O74">
         <v>1.25</v>
@@ -19831,16 +19831,16 @@
         <v>1.74</v>
       </c>
       <c r="R74">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S74">
         <v>2.82</v>
       </c>
       <c r="T74">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U74">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V74">
         <v>1.98</v>
@@ -19849,91 +19849,91 @@
         <v>1.34</v>
       </c>
       <c r="X74">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y74">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z74">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA74">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB74">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC74">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD74">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE74">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF74">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG74">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH74">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI74">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ74">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK74">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL74">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM74">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN74">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO74">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP74">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ74">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR74">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS74">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT74">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU74">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV74">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW74">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AX74">
         <v>1.01</v>
       </c>
       <c r="AY74">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ74">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA74">
         <v>1.01</v>
@@ -19954,7 +19954,7 @@
         <v>1.01</v>
       </c>
       <c r="BG74">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BH74">
         <v>1000</v>
@@ -20297,7 +20297,7 @@
         <v>3.95</v>
       </c>
       <c r="L76">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M76">
         <v>1.07</v>
@@ -20315,7 +20315,7 @@
         <v>1.89</v>
       </c>
       <c r="R76">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S76">
         <v>3.3</v>
@@ -20533,7 +20533,7 @@
         <v>5.1</v>
       </c>
       <c r="J77">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K77">
         <v>3.5</v>
@@ -20545,7 +20545,7 @@
         <v>1.04</v>
       </c>
       <c r="N77">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O77">
         <v>1.04</v>
@@ -21041,7 +21041,7 @@
         <v>1.93</v>
       </c>
       <c r="R79">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S79">
         <v>3.4</v>
@@ -21262,7 +21262,7 @@
         <v>3.35</v>
       </c>
       <c r="K80">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L80">
         <v>1.35</v>
@@ -21271,7 +21271,7 @@
         <v>1.01</v>
       </c>
       <c r="N80">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O80">
         <v>1.36</v>
@@ -21522,7 +21522,7 @@
         <v>2</v>
       </c>
       <c r="Q81">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R81">
         <v>1.38</v>
@@ -21561,16 +21561,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD81">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AE81">
         <v>42</v>
       </c>
       <c r="AF81">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AG81">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH81">
         <v>970</v>
@@ -21603,10 +21603,10 @@
         <v>11</v>
       </c>
       <c r="AR81">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS81">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT81">
         <v>9.4</v>
@@ -21618,7 +21618,7 @@
         <v>12</v>
       </c>
       <c r="AW81">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AX81">
         <v>14</v>
@@ -21630,25 +21630,25 @@
         <v>14.5</v>
       </c>
       <c r="BA81">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BB81">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC81">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BD81">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BE81">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF81">
         <v>14</v>
       </c>
       <c r="BG81">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="BH81">
         <v>1000</v>
@@ -21740,7 +21740,7 @@
         <v>4</v>
       </c>
       <c r="I82">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="J82">
         <v>3.55</v>
@@ -21749,7 +21749,7 @@
         <v>8.6</v>
       </c>
       <c r="L82">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M82">
         <v>1.01</v>
@@ -21767,16 +21767,16 @@
         <v>1.73</v>
       </c>
       <c r="R82">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="S82">
         <v>2.26</v>
       </c>
       <c r="T82">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U82">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V82">
         <v>1.09</v>
@@ -22003,13 +22003,13 @@
         <v>1.18</v>
       </c>
       <c r="P83">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q83">
         <v>1.18</v>
       </c>
       <c r="R83">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S83">
         <v>1.18</v>
@@ -22215,13 +22215,13 @@
         <v>469</v>
       </c>
       <c r="F84">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G84">
         <v>970</v>
       </c>
       <c r="H84">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I84">
         <v>2.56</v>
@@ -22245,7 +22245,7 @@
         <v>1.16</v>
       </c>
       <c r="P84">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Q84">
         <v>1.16</v>
@@ -22481,7 +22481,7 @@
         <v>1.01</v>
       </c>
       <c r="N85">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O85">
         <v>1.15</v>
@@ -22729,7 +22729,7 @@
         <v>1.14</v>
       </c>
       <c r="P86">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Q86">
         <v>1.14</v>
@@ -22971,16 +22971,16 @@
         <v>1.17</v>
       </c>
       <c r="P87">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q87">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="R87">
         <v>1.24</v>
       </c>
       <c r="S87">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="T87">
         <v>1.11</v>
@@ -23425,7 +23425,7 @@
         <v>474</v>
       </c>
       <c r="F89">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G89">
         <v>2.78</v>
@@ -23440,7 +23440,7 @@
         <v>3.1</v>
       </c>
       <c r="K89">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L89">
         <v>1.46</v>
@@ -23455,7 +23455,7 @@
         <v>1.02</v>
       </c>
       <c r="P89">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q89">
         <v>2.48</v>
@@ -23817,7 +23817,7 @@
         <v>21</v>
       </c>
       <c r="BD90">
-        <v>28</v>
+        <v>7.6</v>
       </c>
       <c r="BE90">
         <v>8.4</v>
@@ -24172,13 +24172,13 @@
         <v>1.31</v>
       </c>
       <c r="M92">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N92">
         <v>3.7</v>
       </c>
       <c r="O92">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="P92">
         <v>1.99</v>
@@ -24193,10 +24193,10 @@
         <v>2.58</v>
       </c>
       <c r="T92">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U92">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V92">
         <v>1.96</v>
@@ -24322,7 +24322,7 @@
         <v>13.5</v>
       </c>
       <c r="BK92">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BL92">
         <v>1000</v>
@@ -24334,7 +24334,7 @@
         <v>10</v>
       </c>
       <c r="BO92">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP92">
         <v>46</v>
@@ -24361,7 +24361,7 @@
         <v>1.72</v>
       </c>
       <c r="BX92">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY92">
         <v>1.79</v>
@@ -24426,7 +24426,7 @@
         <v>1.86</v>
       </c>
       <c r="Q93">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R93">
         <v>1.35</v>
@@ -24447,7 +24447,7 @@
         <v>1.83</v>
       </c>
       <c r="X93">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y93">
         <v>14</v>
@@ -24468,10 +24468,10 @@
         <v>16</v>
       </c>
       <c r="AE93">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF93">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG93">
         <v>11</v>
@@ -24635,13 +24635,13 @@
         <v>479</v>
       </c>
       <c r="F94">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G94">
-        <v>2.78</v>
+        <v>2.64</v>
       </c>
       <c r="H94">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="I94">
         <v>3.1</v>
@@ -24659,19 +24659,19 @@
         <v>1.06</v>
       </c>
       <c r="N94">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="O94">
         <v>1.29</v>
       </c>
       <c r="P94">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="Q94">
         <v>1.85</v>
       </c>
       <c r="R94">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S94">
         <v>3.15</v>
@@ -24680,13 +24680,13 @@
         <v>1.69</v>
       </c>
       <c r="U94">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="V94">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W94">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="X94">
         <v>18.5</v>
@@ -24731,7 +24731,7 @@
         <v>34</v>
       </c>
       <c r="AL94">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM94">
         <v>100</v>
@@ -24752,7 +24752,7 @@
         <v>16</v>
       </c>
       <c r="AS94">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AT94">
         <v>9.199999999999999</v>
@@ -24764,7 +24764,7 @@
         <v>10</v>
       </c>
       <c r="AW94">
-        <v>5.7</v>
+        <v>9.4</v>
       </c>
       <c r="AX94">
         <v>15</v>
@@ -24776,19 +24776,19 @@
         <v>14</v>
       </c>
       <c r="BA94">
-        <v>5.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB94">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BC94">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD94">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BE94">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BF94">
         <v>14.5</v>
@@ -25152,13 +25152,13 @@
         <v>2.18</v>
       </c>
       <c r="Q96">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R96">
         <v>1.47</v>
       </c>
       <c r="S96">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T96">
         <v>1.71</v>
@@ -25848,7 +25848,7 @@
         <v>1.86</v>
       </c>
       <c r="G99">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H99">
         <v>3.95</v>
@@ -25878,7 +25878,7 @@
         <v>2.06</v>
       </c>
       <c r="Q99">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R99">
         <v>1.41</v>
@@ -26096,10 +26096,10 @@
         <v>6</v>
       </c>
       <c r="I100">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J100">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K100">
         <v>8.800000000000001</v>
@@ -26111,22 +26111,22 @@
         <v>1.01</v>
       </c>
       <c r="N100">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="O100">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P100">
         <v>2.6</v>
       </c>
       <c r="Q100">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="R100">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S100">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="T100">
         <v>1.11</v>
@@ -26344,7 +26344,7 @@
         <v>4.1</v>
       </c>
       <c r="K101">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L101">
         <v>1.27</v>
@@ -26395,7 +26395,7 @@
         <v>150</v>
       </c>
       <c r="AB101">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC101">
         <v>12</v>
@@ -26434,7 +26434,7 @@
         <v>9.6</v>
       </c>
       <c r="AO101">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP101">
         <v>14</v>
@@ -26598,7 +26598,7 @@
         <v>2.5</v>
       </c>
       <c r="O102">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P102">
         <v>2.02</v>
@@ -26840,22 +26840,22 @@
         <v>4.7</v>
       </c>
       <c r="O103">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P103">
         <v>2.3</v>
       </c>
       <c r="Q103">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R103">
         <v>1.51</v>
       </c>
       <c r="S103">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T103">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U103">
         <v>2.38</v>
@@ -26912,7 +26912,7 @@
         <v>30</v>
       </c>
       <c r="AM103">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN103">
         <v>11.5</v>
@@ -26930,7 +26930,7 @@
         <v>25</v>
       </c>
       <c r="AS103">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="AT103">
         <v>10.5</v>
@@ -27309,7 +27309,7 @@
         <v>3.9</v>
       </c>
       <c r="J105">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K105">
         <v>4.3</v>
@@ -27569,13 +27569,13 @@
         <v>1.18</v>
       </c>
       <c r="P106">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q106">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="R106">
-        <v>1.39</v>
+        <v>1.06</v>
       </c>
       <c r="S106">
         <v>2.38</v>
@@ -27611,7 +27611,7 @@
         <v>14.5</v>
       </c>
       <c r="AD106">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE106">
         <v>1000</v>
@@ -27907,7 +27907,7 @@
         <v>12.5</v>
       </c>
       <c r="AV107">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="AW107">
         <v>7.8</v>
@@ -28053,10 +28053,10 @@
         <v>1.09</v>
       </c>
       <c r="P108">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="Q108">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="R108">
         <v>1.8</v>
@@ -28271,13 +28271,13 @@
         <v>990</v>
       </c>
       <c r="H109">
-        <v>1.05</v>
+        <v>1.58</v>
       </c>
       <c r="I109">
         <v>10</v>
       </c>
       <c r="J109">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K109">
         <v>950</v>
@@ -28316,7 +28316,7 @@
         <v>1.11</v>
       </c>
       <c r="W109">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X109">
         <v>1000</v>
@@ -28997,7 +28997,7 @@
         <v>1.77</v>
       </c>
       <c r="H112">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I112">
         <v>6.4</v>
@@ -29018,13 +29018,13 @@
         <v>4.2</v>
       </c>
       <c r="O112">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P112">
         <v>2.1</v>
       </c>
       <c r="Q112">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R112">
         <v>1.43</v>
@@ -29033,10 +29033,10 @@
         <v>2.82</v>
       </c>
       <c r="T112">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U112">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V112">
         <v>1.19</v>
@@ -29102,7 +29102,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ112">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR112">
         <v>1.01</v>
@@ -29123,7 +29123,7 @@
         <v>1.01</v>
       </c>
       <c r="AX112">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY112">
         <v>8.6</v>
@@ -29147,7 +29147,7 @@
         <v>1.01</v>
       </c>
       <c r="BF112">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG112">
         <v>1.01</v>
@@ -29266,7 +29266,7 @@
         <v>1.25</v>
       </c>
       <c r="Q113">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="R113">
         <v>1.25</v>
@@ -29484,13 +29484,13 @@
         <v>2.1</v>
       </c>
       <c r="I114">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J114">
         <v>4</v>
       </c>
       <c r="K114">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L114">
         <v>1.01</v>
@@ -29499,7 +29499,7 @@
         <v>1.02</v>
       </c>
       <c r="N114">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="O114">
         <v>1.11</v>
@@ -29523,7 +29523,7 @@
         <v>1.01</v>
       </c>
       <c r="V114">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W114">
         <v>1.42</v>
@@ -29717,22 +29717,22 @@
         <v>500</v>
       </c>
       <c r="F115">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G115">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H115">
         <v>6.2</v>
       </c>
       <c r="I115">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J115">
         <v>5.1</v>
       </c>
       <c r="K115">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L115">
         <v>1.01</v>
@@ -29753,7 +29753,7 @@
         <v>1.43</v>
       </c>
       <c r="R115">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="S115">
         <v>2.08</v>
@@ -29768,7 +29768,7 @@
         <v>1.17</v>
       </c>
       <c r="W115">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="X115">
         <v>32</v>
@@ -29780,7 +29780,7 @@
         <v>70</v>
       </c>
       <c r="AA115">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB115">
         <v>16</v>
@@ -29789,7 +29789,7 @@
         <v>14</v>
       </c>
       <c r="AD115">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE115">
         <v>70</v>
@@ -29801,7 +29801,7 @@
         <v>10.5</v>
       </c>
       <c r="AH115">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI115">
         <v>60</v>
@@ -29822,7 +29822,7 @@
         <v>5.6</v>
       </c>
       <c r="AO115">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AP115">
         <v>27</v>
@@ -29837,7 +29837,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AT115">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU115">
         <v>11.5</v>
@@ -29858,7 +29858,7 @@
         <v>16.5</v>
       </c>
       <c r="BA115">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB115">
         <v>14</v>
@@ -29876,7 +29876,7 @@
         <v>4.6</v>
       </c>
       <c r="BG115">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH115">
         <v>1000</v>
@@ -29977,16 +29977,16 @@
         <v>4</v>
       </c>
       <c r="L116">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M116">
         <v>1.05</v>
       </c>
       <c r="N116">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O116">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P116">
         <v>2.08</v>
@@ -30070,7 +30070,7 @@
         <v>13</v>
       </c>
       <c r="AQ116">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR116">
         <v>14.5</v>
@@ -30109,16 +30109,16 @@
         <v>4.7</v>
       </c>
       <c r="BD116">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE116">
         <v>4.4</v>
       </c>
       <c r="BF116">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BG116">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BH116">
         <v>1000</v>
@@ -30142,7 +30142,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BO116">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP116">
         <v>28</v>
@@ -30160,7 +30160,7 @@
         <v>8.6</v>
       </c>
       <c r="BU116">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BV116">
         <v>29</v>
@@ -30207,13 +30207,13 @@
         <v>2.64</v>
       </c>
       <c r="H117">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I117">
         <v>3.25</v>
       </c>
       <c r="J117">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K117">
         <v>3.55</v>
@@ -30225,7 +30225,7 @@
         <v>1.07</v>
       </c>
       <c r="N117">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O117">
         <v>1.34</v>
@@ -30255,52 +30255,52 @@
         <v>1.6</v>
       </c>
       <c r="X117">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y117">
+        <v>12</v>
+      </c>
+      <c r="Z117">
+        <v>21</v>
+      </c>
+      <c r="AA117">
+        <v>55</v>
+      </c>
+      <c r="AB117">
+        <v>10.5</v>
+      </c>
+      <c r="AC117">
+        <v>8</v>
+      </c>
+      <c r="AD117">
         <v>13.5</v>
       </c>
-      <c r="Z117">
-        <v>24</v>
-      </c>
-      <c r="AA117">
-        <v>60</v>
-      </c>
-      <c r="AB117">
+      <c r="AE117">
+        <v>38</v>
+      </c>
+      <c r="AF117">
+        <v>16.5</v>
+      </c>
+      <c r="AG117">
         <v>12</v>
-      </c>
-      <c r="AC117">
-        <v>9</v>
-      </c>
-      <c r="AD117">
-        <v>14</v>
-      </c>
-      <c r="AE117">
-        <v>42</v>
-      </c>
-      <c r="AF117">
-        <v>17</v>
-      </c>
-      <c r="AG117">
-        <v>12.5</v>
       </c>
       <c r="AH117">
         <v>19</v>
       </c>
       <c r="AI117">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ117">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK117">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AL117">
         <v>44</v>
       </c>
       <c r="AM117">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN117">
         <v>28</v>
@@ -30312,55 +30312,55 @@
         <v>12</v>
       </c>
       <c r="AQ117">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR117">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS117">
-        <v>5.8</v>
+        <v>44</v>
       </c>
       <c r="AT117">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU117">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV117">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW117">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="AX117">
         <v>14</v>
       </c>
       <c r="AY117">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ117">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA117">
-        <v>5.8</v>
+        <v>40</v>
       </c>
       <c r="BB117">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="BC117">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD117">
-        <v>5.6</v>
+        <v>36</v>
       </c>
       <c r="BE117">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="BF117">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG117">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="BH117">
         <v>1000</v>
@@ -30700,7 +30700,7 @@
         <v>4.6</v>
       </c>
       <c r="K119">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L119">
         <v>1.01</v>
@@ -30933,7 +30933,7 @@
         <v>7.4</v>
       </c>
       <c r="H120">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="I120">
         <v>1.69</v>
@@ -31169,10 +31169,10 @@
         <v>506</v>
       </c>
       <c r="F121">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="G121">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H121">
         <v>2.56</v>
@@ -31181,10 +31181,10 @@
         <v>3.15</v>
       </c>
       <c r="J121">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K121">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="L121">
         <v>1.34</v>
@@ -31423,7 +31423,7 @@
         <v>990</v>
       </c>
       <c r="J122">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="K122">
         <v>950</v>
@@ -31435,13 +31435,13 @@
         <v>1.01</v>
       </c>
       <c r="N122">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O122">
         <v>1.17</v>
       </c>
       <c r="P122">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q122">
         <v>1.17</v>
@@ -31925,13 +31925,13 @@
         <v>1.24</v>
       </c>
       <c r="P124">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Q124">
         <v>1.24</v>
       </c>
       <c r="R124">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
       <c r="S124">
         <v>1.24</v>
@@ -32302,19 +32302,19 @@
         <v>1000</v>
       </c>
       <c r="BI125">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BJ125">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BK125">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="BL125">
         <v>1000</v>
       </c>
       <c r="BM125">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BN125">
         <v>6.4</v>
@@ -32326,13 +32326,13 @@
         <v>22</v>
       </c>
       <c r="BQ125">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BR125">
         <v>44</v>
       </c>
       <c r="BS125">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="BT125">
         <v>9.800000000000001</v>
@@ -32344,19 +32344,19 @@
         <v>46</v>
       </c>
       <c r="BW125">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="BX125">
         <v>1000</v>
       </c>
       <c r="BY125">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="BZ125">
         <v>38</v>
       </c>
       <c r="CA125">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="CB125" t="s">
         <v>587</v>
@@ -32382,19 +32382,19 @@
         <v>4.4</v>
       </c>
       <c r="G126">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H126">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I126">
         <v>1.95</v>
       </c>
       <c r="J126">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K126">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L126">
         <v>1.01</v>
@@ -32403,7 +32403,7 @@
         <v>1.07</v>
       </c>
       <c r="N126">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O126">
         <v>1.31</v>
@@ -32887,7 +32887,7 @@
         <v>1.01</v>
       </c>
       <c r="N128">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O128">
         <v>1.3</v>
@@ -33105,16 +33105,16 @@
         <v>514</v>
       </c>
       <c r="F129">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="G129">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H129">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="I129">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="J129">
         <v>3.35</v>
@@ -33129,10 +33129,10 @@
         <v>1.01</v>
       </c>
       <c r="N129">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O129">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P129">
         <v>1.94</v>
@@ -33141,10 +33141,10 @@
         <v>1.96</v>
       </c>
       <c r="R129">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="S129">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T129">
         <v>1.11</v>
@@ -33153,10 +33153,10 @@
         <v>1.11</v>
       </c>
       <c r="V129">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="W129">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X129">
         <v>1000</v>
@@ -33347,7 +33347,7 @@
         <v>515</v>
       </c>
       <c r="F130">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G130">
         <v>2.3</v>
@@ -33362,7 +33362,7 @@
         <v>3.85</v>
       </c>
       <c r="K130">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="L130">
         <v>1.01</v>
@@ -33595,16 +33595,16 @@
         <v>2.96</v>
       </c>
       <c r="H131">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="I131">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J131">
         <v>3.35</v>
       </c>
       <c r="K131">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L131">
         <v>1.01</v>
@@ -33622,7 +33622,7 @@
         <v>1.94</v>
       </c>
       <c r="Q131">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R131">
         <v>1.36</v>
@@ -33637,7 +33637,7 @@
         <v>1.01</v>
       </c>
       <c r="V131">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W131">
         <v>1.51</v>
@@ -33849,13 +33849,13 @@
         <v>5.9</v>
       </c>
       <c r="L132">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M132">
         <v>1.03</v>
       </c>
       <c r="N132">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O132">
         <v>1.18</v>
@@ -33870,13 +33870,13 @@
         <v>1.48</v>
       </c>
       <c r="S132">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="T132">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="U132">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V132">
         <v>1.29</v>
@@ -34112,7 +34112,7 @@
         <v>1.48</v>
       </c>
       <c r="S133">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T133">
         <v>1.82</v>
@@ -34339,7 +34339,7 @@
         <v>1.07</v>
       </c>
       <c r="N134">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O134">
         <v>1.32</v>
@@ -34348,16 +34348,16 @@
         <v>1.97</v>
       </c>
       <c r="Q134">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R134">
         <v>1.38</v>
       </c>
       <c r="S134">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T134">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U134">
         <v>2.2</v>
@@ -34420,7 +34420,7 @@
         <v>27</v>
       </c>
       <c r="AO134">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AP134">
         <v>12.5</v>
@@ -34444,7 +34444,7 @@
         <v>10.5</v>
       </c>
       <c r="AW134">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX134">
         <v>15</v>
@@ -34456,19 +34456,19 @@
         <v>14</v>
       </c>
       <c r="BA134">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB134">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC134">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD134">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE134">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF134">
         <v>17.5</v>
@@ -34602,7 +34602,7 @@
         <v>1.58</v>
       </c>
       <c r="U135">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="V135">
         <v>1.94</v>
@@ -34617,7 +34617,7 @@
         <v>14.5</v>
       </c>
       <c r="Z135">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA135">
         <v>32</v>
@@ -34632,10 +34632,10 @@
         <v>15</v>
       </c>
       <c r="AE135">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF135">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG135">
         <v>23</v>
@@ -34650,7 +34650,7 @@
         <v>100</v>
       </c>
       <c r="AK135">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AL135">
         <v>70</v>
@@ -34689,7 +34689,7 @@
         <v>2.24</v>
       </c>
       <c r="AX135">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AY135">
         <v>2.2</v>
@@ -34758,7 +34758,7 @@
         <v>6.4</v>
       </c>
       <c r="BU135">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BV135">
         <v>19</v>
@@ -35074,7 +35074,7 @@
         <v>3.1</v>
       </c>
       <c r="Q137">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="R137">
         <v>1.87</v>
@@ -35146,10 +35146,10 @@
         <v>17.5</v>
       </c>
       <c r="AO137">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AP137">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AQ137">
         <v>14.5</v>
@@ -35173,7 +35173,7 @@
         <v>17</v>
       </c>
       <c r="AX137">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AY137">
         <v>11.5</v>
@@ -35185,16 +35185,16 @@
         <v>18</v>
       </c>
       <c r="BB137">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="BC137">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BD137">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BE137">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BF137">
         <v>11.5</v>
@@ -35313,7 +35313,7 @@
         <v>1.23</v>
       </c>
       <c r="P138">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="Q138">
         <v>1.23</v>
@@ -35540,16 +35540,16 @@
         <v>3.2</v>
       </c>
       <c r="K139">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L139">
         <v>1.01</v>
       </c>
       <c r="M139">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N139">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O139">
         <v>1.25</v>
@@ -35558,7 +35558,7 @@
         <v>2.1</v>
       </c>
       <c r="Q139">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R139">
         <v>1.4</v>
@@ -35797,7 +35797,7 @@
         <v>1.25</v>
       </c>
       <c r="P140">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="Q140">
         <v>1.73</v>
@@ -35818,7 +35818,7 @@
         <v>1.43</v>
       </c>
       <c r="W140">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X140">
         <v>1000</v>
@@ -36015,16 +36015,16 @@
         <v>3.15</v>
       </c>
       <c r="H141">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I141">
-        <v>2.74</v>
+        <v>3.25</v>
       </c>
       <c r="J141">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K141">
-        <v>100</v>
+        <v>3.65</v>
       </c>
       <c r="L141">
         <v>1.01</v>
@@ -36033,10 +36033,10 @@
         <v>1.01</v>
       </c>
       <c r="N141">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="O141">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P141">
         <v>1.7</v>
@@ -36057,7 +36057,7 @@
         <v>1.01</v>
       </c>
       <c r="V141">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W141">
         <v>1.47</v>
@@ -36251,7 +36251,7 @@
         <v>527</v>
       </c>
       <c r="F142">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G142">
         <v>2.4</v>
@@ -36275,7 +36275,7 @@
         <v>1.05</v>
       </c>
       <c r="N142">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="O142">
         <v>1.24</v>
@@ -36293,7 +36293,7 @@
         <v>2.66</v>
       </c>
       <c r="T142">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U142">
         <v>1.01</v>
@@ -37016,7 +37016,7 @@
         <v>1.18</v>
       </c>
       <c r="S145">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="T145">
         <v>1.11</v>
@@ -37243,28 +37243,28 @@
         <v>1.07</v>
       </c>
       <c r="N146">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O146">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P146">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q146">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R146">
         <v>1.35</v>
       </c>
       <c r="S146">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="T146">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="U146">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="V146">
         <v>1.43</v>
@@ -37273,112 +37273,112 @@
         <v>1.61</v>
       </c>
       <c r="X146">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y146">
+        <v>12.5</v>
+      </c>
+      <c r="Z146">
+        <v>22</v>
+      </c>
+      <c r="AA146">
+        <v>60</v>
+      </c>
+      <c r="AB146">
+        <v>10.5</v>
+      </c>
+      <c r="AC146">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD146">
         <v>14.5</v>
       </c>
-      <c r="Z146">
-        <v>27</v>
-      </c>
-      <c r="AA146">
-        <v>70</v>
-      </c>
-      <c r="AB146">
-        <v>12</v>
-      </c>
-      <c r="AC146">
-        <v>9.6</v>
-      </c>
-      <c r="AD146">
+      <c r="AE146">
+        <v>40</v>
+      </c>
+      <c r="AF146">
         <v>17</v>
       </c>
-      <c r="AE146">
-        <v>48</v>
-      </c>
-      <c r="AF146">
-        <v>20</v>
-      </c>
       <c r="AG146">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH146">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI146">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ146">
+        <v>38</v>
+      </c>
+      <c r="AK146">
+        <v>30</v>
+      </c>
+      <c r="AL146">
         <v>44</v>
       </c>
-      <c r="AK146">
-        <v>36</v>
-      </c>
-      <c r="AL146">
-        <v>50</v>
-      </c>
       <c r="AM146">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN146">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO146">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP146">
-        <v>2.76</v>
+        <v>11.5</v>
       </c>
       <c r="AQ146">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="AR146">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS146">
-        <v>2.66</v>
+        <v>7.4</v>
       </c>
       <c r="AT146">
-        <v>2.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU146">
-        <v>2.14</v>
+        <v>6.8</v>
       </c>
       <c r="AV146">
-        <v>2.38</v>
+        <v>11.5</v>
       </c>
       <c r="AW146">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AX146">
-        <v>2.42</v>
+        <v>13.5</v>
       </c>
       <c r="AY146">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="AZ146">
-        <v>2.46</v>
+        <v>15</v>
       </c>
       <c r="BA146">
-        <v>2.64</v>
+        <v>7.2</v>
       </c>
       <c r="BB146">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC146">
-        <v>2.56</v>
+        <v>6.6</v>
       </c>
       <c r="BD146">
-        <v>2.62</v>
+        <v>34</v>
       </c>
       <c r="BE146">
-        <v>2.76</v>
+        <v>7.8</v>
       </c>
       <c r="BF146">
-        <v>2.76</v>
+        <v>17.5</v>
       </c>
       <c r="BG146">
-        <v>2.76</v>
+        <v>6.8</v>
       </c>
       <c r="BH146">
         <v>1000</v>
@@ -37703,19 +37703,19 @@
         <v>533</v>
       </c>
       <c r="F148">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G148">
         <v>990</v>
       </c>
       <c r="H148">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="I148">
         <v>990</v>
       </c>
       <c r="J148">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="K148">
         <v>500</v>
@@ -37945,7 +37945,7 @@
         <v>534</v>
       </c>
       <c r="F149">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G149">
         <v>1.77</v>
@@ -38110,19 +38110,19 @@
         <v>1000</v>
       </c>
       <c r="BI149">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="BJ149">
         <v>13.5</v>
       </c>
       <c r="BK149">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="BL149">
         <v>1000</v>
       </c>
       <c r="BM149">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="BN149">
         <v>6.4</v>
@@ -38134,34 +38134,34 @@
         <v>15.5</v>
       </c>
       <c r="BQ149">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="BR149">
         <v>30</v>
       </c>
       <c r="BS149">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="BT149">
         <v>13</v>
       </c>
       <c r="BU149">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="BV149">
         <v>1000</v>
       </c>
       <c r="BW149">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="BX149">
         <v>1000</v>
       </c>
       <c r="BY149">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="BZ149">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA149">
         <v>1.79</v>
@@ -38202,7 +38202,7 @@
         <v>3.6</v>
       </c>
       <c r="K150">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="L150">
         <v>1.01</v>
@@ -38432,13 +38432,13 @@
         <v>1.92</v>
       </c>
       <c r="G151">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H151">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I151">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J151">
         <v>3.8</v>
@@ -38450,145 +38450,145 @@
         <v>1.01</v>
       </c>
       <c r="M151">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N151">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O151">
         <v>1.3</v>
       </c>
       <c r="P151">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q151">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R151">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S151">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T151">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U151">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="V151">
         <v>1.27</v>
       </c>
       <c r="W151">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="X151">
         <v>14.5</v>
       </c>
       <c r="Y151">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z151">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA151">
         <v>110</v>
       </c>
       <c r="AB151">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC151">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD151">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE151">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF151">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG151">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH151">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI151">
         <v>70</v>
       </c>
       <c r="AJ151">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AK151">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL151">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM151">
         <v>110</v>
       </c>
       <c r="AN151">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO151">
         <v>60</v>
       </c>
       <c r="AP151">
-        <v>4.9</v>
+        <v>13.5</v>
       </c>
       <c r="AQ151">
         <v>13.5</v>
       </c>
       <c r="AR151">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS151">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="AT151">
         <v>8</v>
       </c>
       <c r="AU151">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV151">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW151">
-        <v>6.6</v>
+        <v>48</v>
       </c>
       <c r="AX151">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY151">
         <v>9</v>
       </c>
       <c r="AZ151">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA151">
-        <v>6.6</v>
+        <v>50</v>
       </c>
       <c r="BB151">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC151">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD151">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BE151">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="BF151">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG151">
-        <v>6.6</v>
+        <v>44</v>
       </c>
       <c r="BH151">
         <v>1000</v>
@@ -38680,22 +38680,22 @@
         <v>5.1</v>
       </c>
       <c r="I152">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J152">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="K152">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="L152">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M152">
         <v>1.01</v>
       </c>
       <c r="N152">
-        <v>2.76</v>
+        <v>1.1</v>
       </c>
       <c r="O152">
         <v>1.37</v>
@@ -38707,7 +38707,7 @@
         <v>2.12</v>
       </c>
       <c r="R152">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="S152">
         <v>3.75</v>
@@ -38719,7 +38719,7 @@
         <v>1.11</v>
       </c>
       <c r="V152">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W152">
         <v>2.22</v>
@@ -38928,7 +38928,7 @@
         <v>3.95</v>
       </c>
       <c r="K153">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L153">
         <v>1.32</v>
@@ -38943,7 +38943,7 @@
         <v>1.25</v>
       </c>
       <c r="P153">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q153">
         <v>1.78</v>
@@ -38955,7 +38955,7 @@
         <v>2.92</v>
       </c>
       <c r="T153">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U153">
         <v>1.11</v>
@@ -39397,13 +39397,13 @@
         <v>540</v>
       </c>
       <c r="F155">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G155">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H155">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I155">
         <v>1000</v>
@@ -39412,7 +39412,7 @@
         <v>3.05</v>
       </c>
       <c r="K155">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L155">
         <v>0</v>
@@ -39639,7 +39639,7 @@
         <v>541</v>
       </c>
       <c r="F156">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G156">
         <v>2.34</v>
@@ -39648,13 +39648,13 @@
         <v>3.9</v>
       </c>
       <c r="I156">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J156">
         <v>3.05</v>
       </c>
       <c r="K156">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L156">
         <v>1.01</v>
@@ -39687,7 +39687,7 @@
         <v>1.11</v>
       </c>
       <c r="V156">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W156">
         <v>1.74</v>
@@ -39884,7 +39884,7 @@
         <v>1.04</v>
       </c>
       <c r="G157">
-        <v>120</v>
+        <v>990</v>
       </c>
       <c r="H157">
         <v>1.05</v>
@@ -39893,7 +39893,7 @@
         <v>990</v>
       </c>
       <c r="J157">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K157">
         <v>950</v>
@@ -40126,7 +40126,7 @@
         <v>1.23</v>
       </c>
       <c r="G158">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H158">
         <v>8.4</v>
@@ -40619,13 +40619,13 @@
         <v>16.5</v>
       </c>
       <c r="J160">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K160">
         <v>10.5</v>
       </c>
       <c r="L160">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M160">
         <v>1.01</v>
@@ -40673,7 +40673,7 @@
         <v>560</v>
       </c>
       <c r="AB160">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AC160">
         <v>25</v>
@@ -40685,7 +40685,7 @@
         <v>170</v>
       </c>
       <c r="AF160">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="AG160">
         <v>13.5</v>
@@ -40715,16 +40715,16 @@
         <v>130</v>
       </c>
       <c r="AP160">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AQ160">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AR160">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AS160">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AT160">
         <v>17.5</v>
@@ -40736,7 +40736,7 @@
         <v>38</v>
       </c>
       <c r="AW160">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AX160">
         <v>10</v>
@@ -40745,28 +40745,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ160">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA160">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BB160">
         <v>10.5</v>
       </c>
       <c r="BC160">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD160">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BE160">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BF160">
         <v>2.36</v>
       </c>
       <c r="BG160">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="BH160">
         <v>1000</v>
@@ -40873,13 +40873,13 @@
         <v>1.01</v>
       </c>
       <c r="N161">
+        <v>1.26</v>
+      </c>
+      <c r="O161">
+        <v>1.01</v>
+      </c>
+      <c r="P161">
         <v>1.25</v>
-      </c>
-      <c r="O161">
-        <v>1.01</v>
-      </c>
-      <c r="P161">
-        <v>1.24</v>
       </c>
       <c r="Q161">
         <v>1.02</v>
@@ -41121,7 +41121,7 @@
         <v>1.01</v>
       </c>
       <c r="P162">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q162">
         <v>1.02</v>
@@ -41357,7 +41357,7 @@
         <v>1.01</v>
       </c>
       <c r="N163">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O163">
         <v>1.01</v>
@@ -41599,13 +41599,13 @@
         <v>1.01</v>
       </c>
       <c r="N164">
+        <v>1.26</v>
+      </c>
+      <c r="O164">
+        <v>1.01</v>
+      </c>
+      <c r="P164">
         <v>1.25</v>
-      </c>
-      <c r="O164">
-        <v>1.01</v>
-      </c>
-      <c r="P164">
-        <v>1.24</v>
       </c>
       <c r="Q164">
         <v>1.02</v>
@@ -41847,7 +41847,7 @@
         <v>1.01</v>
       </c>
       <c r="P165">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q165">
         <v>1.02</v>
@@ -42095,7 +42095,7 @@
         <v>1.56</v>
       </c>
       <c r="R166">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S166">
         <v>2.3</v>
@@ -42304,10 +42304,10 @@
         <v>3.95</v>
       </c>
       <c r="G167">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H167">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="I167">
         <v>2.26</v>
@@ -42331,13 +42331,13 @@
         <v>1.43</v>
       </c>
       <c r="P167">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q167">
         <v>2.3</v>
       </c>
       <c r="R167">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S167">
         <v>4.4</v>
@@ -42349,10 +42349,10 @@
         <v>1.86</v>
       </c>
       <c r="V167">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="W167">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X167">
         <v>12</v>
@@ -42367,10 +42367,10 @@
         <v>32</v>
       </c>
       <c r="AB167">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC167">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD167">
         <v>13</v>
@@ -42379,7 +42379,7 @@
         <v>32</v>
       </c>
       <c r="AF167">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG167">
         <v>18</v>
@@ -42391,19 +42391,19 @@
         <v>60</v>
       </c>
       <c r="AJ167">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK167">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AL167">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM167">
         <v>170</v>
       </c>
       <c r="AN167">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AO167">
         <v>26</v>
@@ -42418,10 +42418,10 @@
         <v>10.5</v>
       </c>
       <c r="AS167">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AT167">
-        <v>4.1</v>
+        <v>10.5</v>
       </c>
       <c r="AU167">
         <v>6.6</v>
@@ -42430,34 +42430,34 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW167">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AX167">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AY167">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="AZ167">
         <v>18</v>
       </c>
       <c r="BA167">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB167">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC167">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BD167">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE167">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BF167">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG167">
         <v>17</v>
@@ -42573,7 +42573,7 @@
         <v>1.34</v>
       </c>
       <c r="P168">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q168">
         <v>2.02</v>
@@ -42708,19 +42708,19 @@
         <v>1000</v>
       </c>
       <c r="BI168">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BJ168">
         <v>13</v>
       </c>
       <c r="BK168">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BL168">
         <v>1000</v>
       </c>
       <c r="BM168">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="BN168">
         <v>8</v>
@@ -42729,7 +42729,7 @@
         <v>4.1</v>
       </c>
       <c r="BP168">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ168">
         <v>1.75</v>
@@ -42738,25 +42738,25 @@
         <v>50</v>
       </c>
       <c r="BS168">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BT168">
         <v>7.6</v>
       </c>
       <c r="BU168">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BV168">
         <v>30</v>
       </c>
       <c r="BW168">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="BX168">
         <v>50</v>
       </c>
       <c r="BY168">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BZ168">
         <v>0</v>
@@ -42800,7 +42800,7 @@
         <v>6.4</v>
       </c>
       <c r="K169">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="L169">
         <v>1.2</v>
@@ -42824,7 +42824,7 @@
         <v>1.61</v>
       </c>
       <c r="S169">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T169">
         <v>1.91</v>
@@ -43027,7 +43027,7 @@
         <v>555</v>
       </c>
       <c r="F170">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="G170">
         <v>2.34</v>
@@ -43281,7 +43281,7 @@
         <v>110</v>
       </c>
       <c r="J171">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K171">
         <v>950</v>
@@ -43440,55 +43440,55 @@
         <v>1000</v>
       </c>
       <c r="BK171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BL171">
         <v>1000</v>
       </c>
       <c r="BM171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BN171">
         <v>1000</v>
       </c>
       <c r="BO171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BP171">
         <v>1000</v>
       </c>
       <c r="BQ171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BR171">
         <v>1000</v>
       </c>
       <c r="BS171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BT171">
         <v>1000</v>
       </c>
       <c r="BU171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BV171">
         <v>1000</v>
       </c>
       <c r="BW171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BX171">
         <v>1000</v>
       </c>
       <c r="BY171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BZ171">
         <v>1000</v>
       </c>
       <c r="CA171">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="CB171" t="s">
         <v>587</v>
@@ -43544,10 +43544,10 @@
         <v>2.04</v>
       </c>
       <c r="Q172">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="R172">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S172">
         <v>3.15</v>
@@ -43634,7 +43634,7 @@
         <v>6.4</v>
       </c>
       <c r="AU172">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AV172">
         <v>18.5</v>
@@ -43649,7 +43649,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ172">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA172">
         <v>4.1</v>
@@ -43753,7 +43753,7 @@
         <v>558</v>
       </c>
       <c r="F173">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="G173">
         <v>1.66</v>
@@ -43762,13 +43762,13 @@
         <v>5.5</v>
       </c>
       <c r="I173">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="J173">
         <v>4.3</v>
       </c>
       <c r="K173">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L173">
         <v>1.01</v>
@@ -43945,7 +43945,7 @@
         <v>6.2</v>
       </c>
       <c r="BR173">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BS173">
         <v>13.5</v>
@@ -43972,7 +43972,7 @@
         <v>23</v>
       </c>
       <c r="CA173">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB173" t="s">
         <v>587</v>
@@ -44019,13 +44019,13 @@
         <v>1.01</v>
       </c>
       <c r="N174">
+        <v>1.26</v>
+      </c>
+      <c r="O174">
+        <v>1.01</v>
+      </c>
+      <c r="P174">
         <v>1.25</v>
-      </c>
-      <c r="O174">
-        <v>1.01</v>
-      </c>
-      <c r="P174">
-        <v>1.24</v>
       </c>
       <c r="Q174">
         <v>1.02</v>
@@ -44237,22 +44237,22 @@
         <v>560</v>
       </c>
       <c r="F175">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="G175">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H175">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I175">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J175">
         <v>4.3</v>
       </c>
       <c r="K175">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L175">
         <v>1.01</v>
@@ -44270,7 +44270,7 @@
         <v>2.52</v>
       </c>
       <c r="Q175">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R175">
         <v>1.61</v>
@@ -44288,10 +44288,10 @@
         <v>1.21</v>
       </c>
       <c r="W175">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X175">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Y175">
         <v>26</v>
@@ -44318,10 +44318,10 @@
         <v>13</v>
       </c>
       <c r="AG175">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH175">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI175">
         <v>55</v>
@@ -44366,19 +44366,19 @@
         <v>17.5</v>
       </c>
       <c r="AW175">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX175">
         <v>11</v>
       </c>
       <c r="AY175">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ175">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA175">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB175">
         <v>15</v>
@@ -44387,7 +44387,7 @@
         <v>14</v>
       </c>
       <c r="BD175">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BE175">
         <v>7</v>
@@ -44503,7 +44503,7 @@
         <v>1.01</v>
       </c>
       <c r="N176">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O176">
         <v>1.33</v>
@@ -44730,7 +44730,7 @@
         <v>4.4</v>
       </c>
       <c r="I177">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J177">
         <v>3.45</v>
@@ -44966,7 +44966,7 @@
         <v>2</v>
       </c>
       <c r="G178">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H178">
         <v>3.75</v>
@@ -44993,10 +44993,10 @@
         <v>1.31</v>
       </c>
       <c r="P178">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q178">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="R178">
         <v>1.32</v>
@@ -45235,10 +45235,10 @@
         <v>1.3</v>
       </c>
       <c r="P179">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q179">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R179">
         <v>1.35</v>
@@ -45471,7 +45471,7 @@
         <v>1.01</v>
       </c>
       <c r="N180">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O180">
         <v>1.3</v>
@@ -45480,7 +45480,7 @@
         <v>1.72</v>
       </c>
       <c r="Q180">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R180">
         <v>1.34</v>
@@ -45692,10 +45692,10 @@
         <v>2.56</v>
       </c>
       <c r="G181">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="H181">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I181">
         <v>2.96</v>
@@ -46439,7 +46439,7 @@
         <v>1.06</v>
       </c>
       <c r="N184">
-        <v>2.74</v>
+        <v>3.9</v>
       </c>
       <c r="O184">
         <v>1.28</v>
@@ -46448,7 +46448,7 @@
         <v>2.04</v>
       </c>
       <c r="Q184">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R184">
         <v>1.38</v>
@@ -46657,19 +46657,19 @@
         <v>570</v>
       </c>
       <c r="F185">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G185">
         <v>4.9</v>
       </c>
       <c r="H185">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I185">
         <v>1.95</v>
       </c>
       <c r="J185">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K185">
         <v>4.2</v>
@@ -46687,10 +46687,10 @@
         <v>1.27</v>
       </c>
       <c r="P185">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="Q185">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R185">
         <v>1.37</v>
@@ -47422,7 +47422,7 @@
         <v>1.18</v>
       </c>
       <c r="S188">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T188">
         <v>1.11</v>
@@ -47661,7 +47661,7 @@
         <v>1.51</v>
       </c>
       <c r="R189">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S189">
         <v>2.28</v>
@@ -47909,10 +47909,10 @@
         <v>3.15</v>
       </c>
       <c r="T190">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U190">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="V190">
         <v>1.06</v>
@@ -48109,22 +48109,22 @@
         <v>576</v>
       </c>
       <c r="F191">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="G191">
         <v>990</v>
       </c>
       <c r="H191">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="I191">
         <v>990</v>
       </c>
       <c r="J191">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="K191">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="L191">
         <v>1.01</v>
@@ -48136,7 +48136,7 @@
         <v>1.33</v>
       </c>
       <c r="O191">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="P191">
         <v>1.33</v>
@@ -48148,7 +48148,7 @@
         <v>1.32</v>
       </c>
       <c r="S191">
-        <v>2.06</v>
+        <v>1.15</v>
       </c>
       <c r="T191">
         <v>1.11</v>
@@ -48157,10 +48157,10 @@
         <v>1.11</v>
       </c>
       <c r="V191">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="W191">
-        <v>1.06</v>
+        <v>1.59</v>
       </c>
       <c r="X191">
         <v>1000</v>
@@ -48363,7 +48363,7 @@
         <v>3.65</v>
       </c>
       <c r="J192">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="K192">
         <v>4.3</v>
@@ -48522,55 +48522,55 @@
         <v>1000</v>
       </c>
       <c r="BK192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BL192">
         <v>1000</v>
       </c>
       <c r="BM192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BN192">
         <v>1000</v>
       </c>
       <c r="BO192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BP192">
         <v>1000</v>
       </c>
       <c r="BQ192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BR192">
         <v>1000</v>
       </c>
       <c r="BS192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BT192">
         <v>1000</v>
       </c>
       <c r="BU192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BV192">
         <v>1000</v>
       </c>
       <c r="BW192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BX192">
         <v>1000</v>
       </c>
       <c r="BY192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BZ192">
         <v>1000</v>
       </c>
       <c r="CA192">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="CB192" t="s">
         <v>587</v>
@@ -48593,22 +48593,22 @@
         <v>578</v>
       </c>
       <c r="F193">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G193">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H193">
         <v>3.6</v>
       </c>
       <c r="I193">
-        <v>110</v>
+        <v>5</v>
       </c>
       <c r="J193">
         <v>1.01</v>
       </c>
       <c r="K193">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L193">
         <v>1.01</v>
@@ -48617,7 +48617,7 @@
         <v>1.01</v>
       </c>
       <c r="N193">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="O193">
         <v>1.02</v>
@@ -48635,16 +48635,16 @@
         <v>3.5</v>
       </c>
       <c r="T193">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U193">
         <v>1.83</v>
       </c>
       <c r="V193">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="W193">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X193">
         <v>1000</v>
@@ -48841,55 +48841,55 @@
         <v>2.56</v>
       </c>
       <c r="H194">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I194">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J194">
         <v>3.3</v>
       </c>
       <c r="K194">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L194">
         <v>1.01</v>
       </c>
       <c r="M194">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N194">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O194">
         <v>1.36</v>
       </c>
       <c r="P194">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="Q194">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R194">
         <v>1.18</v>
       </c>
       <c r="S194">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T194">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U194">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V194">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W194">
         <v>1.64</v>
       </c>
       <c r="X194">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y194">
         <v>1000</v>
@@ -48943,58 +48943,58 @@
         <v>1000</v>
       </c>
       <c r="AP194">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AR194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AS194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AT194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AU194">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AV194">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AW194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AX194">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY194">
         <v>1.52</v>
       </c>
       <c r="AZ194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BA194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BB194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BC194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BD194">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BE194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BF194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BG194">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BH194">
         <v>1000</v>
@@ -49101,16 +49101,16 @@
         <v>1.01</v>
       </c>
       <c r="N195">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="O195">
         <v>1.3</v>
       </c>
       <c r="P195">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q195">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R195">
         <v>1.31</v>
@@ -49319,16 +49319,16 @@
         <v>581</v>
       </c>
       <c r="F196">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G196">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="H196">
         <v>1.25</v>
       </c>
       <c r="I196">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="J196">
         <v>6.4</v>
@@ -49343,13 +49343,13 @@
         <v>1.03</v>
       </c>
       <c r="N196">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="O196">
         <v>1.19</v>
       </c>
       <c r="P196">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q196">
         <v>1.58</v>
@@ -49358,7 +49358,7 @@
         <v>1.5</v>
       </c>
       <c r="S196">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="T196">
         <v>1.01</v>
@@ -49367,7 +49367,7 @@
         <v>1.01</v>
       </c>
       <c r="V196">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="W196">
         <v>1.06</v>
@@ -49382,7 +49382,7 @@
         <v>10</v>
       </c>
       <c r="AA196">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AB196">
         <v>70</v>
@@ -49424,58 +49424,58 @@
         <v>1000</v>
       </c>
       <c r="AO196">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP196">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="AQ196">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AR196">
         <v>6.4</v>
       </c>
       <c r="AS196">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AT196">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AU196">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="AV196">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="AW196">
         <v>10.5</v>
       </c>
       <c r="AX196">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="AY196">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="AZ196">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="BA196">
-        <v>2.46</v>
+        <v>3</v>
       </c>
       <c r="BB196">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="BC196">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="BD196">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE196">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="BF196">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="BG196">
         <v>3.1</v>
@@ -49561,19 +49561,19 @@
         <v>582</v>
       </c>
       <c r="F197">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G197">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H197">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="I197">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J197">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K197">
         <v>3.15</v>
@@ -49591,7 +49591,7 @@
         <v>0</v>
       </c>
       <c r="P197">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q197">
         <v>2.78</v>
@@ -49974,55 +49974,55 @@
         <v>1000</v>
       </c>
       <c r="BK198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL198">
         <v>1000</v>
       </c>
       <c r="BM198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN198">
         <v>1000</v>
       </c>
       <c r="BO198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP198">
         <v>1000</v>
       </c>
       <c r="BQ198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR198">
         <v>1000</v>
       </c>
       <c r="BS198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT198">
         <v>1000</v>
       </c>
       <c r="BU198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV198">
         <v>1000</v>
       </c>
       <c r="BW198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX198">
         <v>1000</v>
       </c>
       <c r="BY198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ198">
         <v>1000</v>
       </c>
       <c r="CA198">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB198" t="s">
         <v>587</v>
@@ -50045,10 +50045,10 @@
         <v>584</v>
       </c>
       <c r="F199">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="G199">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H199">
         <v>2.84</v>
@@ -50057,10 +50057,10 @@
         <v>4.8</v>
       </c>
       <c r="J199">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="K199">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L199">
         <v>1.43</v>
@@ -50069,7 +50069,7 @@
         <v>1.01</v>
       </c>
       <c r="N199">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="O199">
         <v>1.24</v>
@@ -50532,10 +50532,10 @@
         <v>2.5</v>
       </c>
       <c r="G201">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H201">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I201">
         <v>3.1</v>
@@ -50544,76 +50544,76 @@
         <v>3.6</v>
       </c>
       <c r="K201">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L201">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M201">
         <v>1.06</v>
       </c>
       <c r="N201">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O201">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P201">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="Q201">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="R201">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="S201">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="T201">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="U201">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V201">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W201">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X201">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y201">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="Z201">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AA201">
         <v>55</v>
       </c>
       <c r="AB201">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AC201">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD201">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE201">
         <v>40</v>
       </c>
       <c r="AF201">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AG201">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AH201">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI201">
         <v>50</v>
@@ -50622,7 +50622,7 @@
         <v>46</v>
       </c>
       <c r="AK201">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AL201">
         <v>46</v>
@@ -50631,64 +50631,64 @@
         <v>95</v>
       </c>
       <c r="AN201">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO201">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP201">
-        <v>2.68</v>
+        <v>14.5</v>
       </c>
       <c r="AQ201">
+        <v>11.5</v>
+      </c>
+      <c r="AR201">
+        <v>18</v>
+      </c>
+      <c r="AS201">
+        <v>32</v>
+      </c>
+      <c r="AT201">
+        <v>10.5</v>
+      </c>
+      <c r="AU201">
+        <v>7.4</v>
+      </c>
+      <c r="AV201">
+        <v>11</v>
+      </c>
+      <c r="AW201">
+        <v>22</v>
+      </c>
+      <c r="AX201">
+        <v>15</v>
+      </c>
+      <c r="AY201">
         <v>10</v>
       </c>
-      <c r="AR201">
-        <v>15</v>
-      </c>
-      <c r="AS201">
-        <v>2.56</v>
-      </c>
-      <c r="AT201">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU201">
-        <v>2.12</v>
-      </c>
-      <c r="AV201">
-        <v>10.5</v>
-      </c>
-      <c r="AW201">
-        <v>2.52</v>
-      </c>
-      <c r="AX201">
-        <v>12.5</v>
-      </c>
-      <c r="AY201">
-        <v>9.6</v>
-      </c>
       <c r="AZ201">
-        <v>2.38</v>
+        <v>13.5</v>
       </c>
       <c r="BA201">
-        <v>2.56</v>
+        <v>28</v>
       </c>
       <c r="BB201">
-        <v>2.54</v>
+        <v>25</v>
       </c>
       <c r="BC201">
         <v>19</v>
       </c>
       <c r="BD201">
-        <v>2.54</v>
+        <v>7</v>
       </c>
       <c r="BE201">
-        <v>2.62</v>
+        <v>7.8</v>
       </c>
       <c r="BF201">
-        <v>2.68</v>
+        <v>16</v>
       </c>
       <c r="BG201">
-        <v>2.68</v>
+        <v>19</v>
       </c>
       <c r="BH201">
         <v>4.6</v>
